--- a/SAM_Opportunities_Report_20260609_PM.xlsx
+++ b/SAM_Opportunities_Report_20260609_PM.xlsx
@@ -14,10 +14,10 @@
     <sheet name="🔧 Specialty Pipeline" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🔴 Action Required'!$B$5:$N$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Watch List'!$B$5:$K$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Full Pipeline'!$B$5:$K$134</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'🔧 Specialty Pipeline'!$B$5:$K$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🔴 Action Required'!$B$5:$N$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Watch List'!$B$5:$K$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Full Pipeline'!$B$5:$K$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'🔧 Specialty Pipeline'!$B$5:$K$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -849,7 +849,7 @@
     <row r="7" ht="32" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>134</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>88</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>88</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>116</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F36" s="23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F38" s="23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
     <row r="46" ht="20" customHeight="1">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>→  50 active Solicitation(s) due within 14 days — immediate bid/no-bid decisions required.</t>
+          <t>→  52 active Solicitation(s) due within 14 days — immediate bid/no-bid decisions required.</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N89"/>
+  <dimension ref="B2:N93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1330,7 +1330,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>All open Solicitations sorted by urgency  ·  84 records  ·  As of June 09, 2026  ·  ★ Gold rows = SDVOSB set-aside</t>
+          <t>All open Solicitations sorted by urgency  ·  88 records  ·  As of June 09, 2026  ·  ★ Gold rows = SDVOSB set-aside</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="D38" s="30" t="inlineStr">
         <is>
-          <t>PAIS WASTE WATER TANK REPLACEMENT</t>
+          <t>Y--PAIS WASTE WATER TANK REPLACEMENT</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="C51" s="20" t="inlineStr">
         <is>
-          <t>140P9726R0002</t>
+          <t>140FS226Q0120</t>
         </is>
       </c>
       <c r="D51" s="33" t="inlineStr">
         <is>
-          <t>Y--GLBA REHAB WATERLINE</t>
+          <t>NM - SW NATIVE ARC - 5-Year BPA for Well Repair</t>
         </is>
       </c>
       <c r="E51" s="20" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="I51" s="20" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="J51" s="20" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>13d</t>
         </is>
       </c>
       <c r="K51" s="18" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>W50S8526BA001</t>
+          <t>140FC126R0025</t>
         </is>
       </c>
       <c r="D52" s="30" t="inlineStr">
         <is>
-          <t>VGLZ 182035 REPAIR BASE PERIMETER ROAD</t>
+          <t>Y--Hasty Point Rice Trunk &amp;</t>
         </is>
       </c>
       <c r="E52" s="17" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>13d</t>
         </is>
       </c>
       <c r="K52" s="18" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="C53" s="20" t="inlineStr">
         <is>
-          <t>140FC326Q0025</t>
+          <t>140P9726R0002</t>
         </is>
       </c>
       <c r="D53" s="33" t="inlineStr">
         <is>
-          <t>NM DEXTER NFHTC POND LINER 12B &amp; 13B</t>
+          <t>Y--GLBA REHAB WATERLINE</t>
         </is>
       </c>
       <c r="E53" s="20" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G53" s="20" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>140P9726Q0044</t>
+          <t>W50S8526BA001</t>
         </is>
       </c>
       <c r="D54" s="30" t="inlineStr">
         <is>
-          <t>EO14398 UST ASSESSMENT &amp; REPORTING - GLBA</t>
+          <t>VGLZ 182035 REPAIR BASE PERIMETER ROAD</t>
         </is>
       </c>
       <c r="E54" s="17" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>213112</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="C55" s="20" t="inlineStr">
         <is>
-          <t>140P6426Q0073</t>
+          <t>140FC326Q0025</t>
         </is>
       </c>
       <c r="D55" s="33" t="inlineStr">
         <is>
-          <t>Crack and Fog Sealing Multiple Locations</t>
+          <t>NM DEXTER NFHTC POND LINER 12B &amp; 13B</t>
         </is>
       </c>
       <c r="E55" s="20" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="F55" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G55" s="20" t="inlineStr">
@@ -4718,22 +4718,22 @@
       </c>
       <c r="H55" s="20" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I55" s="20" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Jun 24, 2026</t>
         </is>
       </c>
       <c r="J55" s="20" t="inlineStr">
         <is>
-          <t>15d</t>
-        </is>
-      </c>
-      <c r="K55" s="41" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
+          <t>14d</t>
+        </is>
+      </c>
+      <c r="K55" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="L55" s="20" t="inlineStr">
@@ -4753,67 +4753,67 @@
       </c>
     </row>
     <row r="56" ht="32" customHeight="1">
-      <c r="B56" s="36" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="C56" s="37" t="inlineStr">
-        <is>
-          <t>W9128F26RA063</t>
-        </is>
-      </c>
-      <c r="D56" s="25" t="inlineStr">
-        <is>
-          <t>Fort Riley Tank CoatingsRepair</t>
-        </is>
-      </c>
-      <c r="E56" s="37" t="inlineStr">
-        <is>
-          <t>Fort Riley, Kansas</t>
-        </is>
-      </c>
-      <c r="F56" s="37" t="inlineStr">
-        <is>
-          <t>237120</t>
-        </is>
-      </c>
-      <c r="G56" s="38" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H56" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I56" s="37" t="inlineStr">
-        <is>
-          <t>Jun 25, 2026</t>
-        </is>
-      </c>
-      <c r="J56" s="37" t="inlineStr">
-        <is>
-          <t>15d</t>
-        </is>
-      </c>
-      <c r="K56" s="41" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
-        </is>
-      </c>
-      <c r="L56" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M56" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N56" s="40" t="inlineStr">
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>140P9726Q0044</t>
+        </is>
+      </c>
+      <c r="D56" s="30" t="inlineStr">
+        <is>
+          <t>EO14398 UST ASSESSMENT &amp; REPORTING - GLBA</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>213112</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="J56" s="17" t="inlineStr">
+        <is>
+          <t>14d</t>
+        </is>
+      </c>
+      <c r="K56" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
+        </is>
+      </c>
+      <c r="L56" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N56" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="C57" s="20" t="inlineStr">
         <is>
-          <t>W911KB26RA039</t>
+          <t>140P6426Q0073</t>
         </is>
       </c>
       <c r="D57" s="33" t="inlineStr">
         <is>
-          <t>FTW506 Life Safety Repairs</t>
+          <t>Crack and Fog Sealing Multiple Locations</t>
         </is>
       </c>
       <c r="E57" s="20" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="F57" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G57" s="20" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H57" s="20" t="inlineStr">
         <is>
-          <t>$18.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="I57" s="20" t="inlineStr">
@@ -4887,47 +4887,47 @@
       </c>
     </row>
     <row r="58" ht="32" customHeight="1">
-      <c r="B58" s="17" t="inlineStr">
+      <c r="B58" s="36" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="C58" s="17" t="inlineStr">
-        <is>
-          <t>W9124D26QA266</t>
-        </is>
-      </c>
-      <c r="D58" s="30" t="inlineStr">
-        <is>
-          <t>USMEPCOM Low Voltage Cable Removal</t>
-        </is>
-      </c>
-      <c r="E58" s="17" t="inlineStr">
-        <is>
-          <t>North Chicago, Illinois</t>
-        </is>
-      </c>
-      <c r="F58" s="17" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="G58" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H58" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I58" s="17" t="inlineStr">
+      <c r="C58" s="37" t="inlineStr">
+        <is>
+          <t>W9128F26RA063</t>
+        </is>
+      </c>
+      <c r="D58" s="25" t="inlineStr">
+        <is>
+          <t>Fort Riley Tank CoatingsRepair</t>
+        </is>
+      </c>
+      <c r="E58" s="37" t="inlineStr">
+        <is>
+          <t>Fort Riley, Kansas</t>
+        </is>
+      </c>
+      <c r="F58" s="37" t="inlineStr">
+        <is>
+          <t>237120</t>
+        </is>
+      </c>
+      <c r="G58" s="38" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H58" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I58" s="37" t="inlineStr">
         <is>
           <t>Jun 25, 2026</t>
         </is>
       </c>
-      <c r="J58" s="17" t="inlineStr">
+      <c r="J58" s="37" t="inlineStr">
         <is>
           <t>15d</t>
         </is>
@@ -4937,17 +4937,17 @@
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L58" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M58" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N58" s="32" t="inlineStr">
+      <c r="L58" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M58" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N58" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -4961,22 +4961,22 @@
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>1605AE-26-Q-00005</t>
+          <t>W911KB26RA039</t>
         </is>
       </c>
       <c r="D59" s="33" t="inlineStr">
         <is>
-          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
+          <t>FTW506 Life Safety Repairs</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F59" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G59" s="20" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H59" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$18.0M</t>
         </is>
       </c>
       <c r="I59" s="20" t="inlineStr">
@@ -5028,22 +5028,22 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0010</t>
+          <t>W9124D26QA266</t>
         </is>
       </c>
       <c r="D60" s="30" t="inlineStr">
         <is>
-          <t>Y--FOMA REPLACE NATURE TRAIL BOARDWALK RS</t>
+          <t>USMEPCOM Low Voltage Cable Removal</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>North Chicago, Illinois</t>
         </is>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
@@ -5058,12 +5058,12 @@
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>Jun 26, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t>16d</t>
+          <t>15d</t>
         </is>
       </c>
       <c r="K60" s="41" t="inlineStr">
@@ -5095,22 +5095,22 @@
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>89503426BWA000066</t>
+          <t>1605AE-26-Q-00005</t>
         </is>
       </c>
       <c r="D61" s="33" t="inlineStr">
         <is>
-          <t>Carpenter Substation Stage 03 South Dakota</t>
+          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
         </is>
       </c>
       <c r="E61" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Atlanta, Georgia</t>
         </is>
       </c>
       <c r="F61" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="G61" s="20" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="I61" s="20" t="inlineStr">
         <is>
-          <t>Jun 26, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="J61" s="20" t="inlineStr">
         <is>
-          <t>16d</t>
+          <t>15d</t>
         </is>
       </c>
       <c r="K61" s="41" t="inlineStr">
@@ -5162,22 +5162,22 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>140P6026Q0025</t>
+          <t>140P5426R0010</t>
         </is>
       </c>
       <c r="D62" s="30" t="inlineStr">
         <is>
-          <t>FOSM - Replace Backflow Prevention Assemblies</t>
+          <t>Y--FOMA REPLACE NATURE TRAIL BOARDWALK RS</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t>Fort Smith, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>140R2026R0007</t>
+          <t>89503426BWA000066</t>
         </is>
       </c>
       <c r="D63" s="33" t="inlineStr">
         <is>
-          <t>CT SWITCHGEAR REPLACEMENT STAMPEDE PP</t>
+          <t>Carpenter Substation Stage 03 South Dakota</t>
         </is>
       </c>
       <c r="E63" s="20" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="F63" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G63" s="20" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="I63" s="20" t="inlineStr">
         <is>
-          <t>Jun 27, 2026</t>
+          <t>Jun 26, 2026</t>
         </is>
       </c>
       <c r="J63" s="20" t="inlineStr">
         <is>
-          <t>17d</t>
+          <t>16d</t>
         </is>
       </c>
       <c r="K63" s="41" t="inlineStr">
@@ -5289,49 +5289,49 @@
       </c>
     </row>
     <row r="64" ht="32" customHeight="1">
-      <c r="B64" s="36" t="inlineStr">
+      <c r="B64" s="17" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="C64" s="37" t="inlineStr">
-        <is>
-          <t>W912QR26RA033</t>
-        </is>
-      </c>
-      <c r="D64" s="25" t="inlineStr">
-        <is>
-          <t>Anniston Army Depot (ANAD) Power Generation and Microgrid Project</t>
-        </is>
-      </c>
-      <c r="E64" s="37" t="inlineStr">
-        <is>
-          <t>Anniston, Alabama</t>
-        </is>
-      </c>
-      <c r="F64" s="37" t="inlineStr">
-        <is>
-          <t>237130</t>
-        </is>
-      </c>
-      <c r="G64" s="38" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H64" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I64" s="37" t="inlineStr">
-        <is>
-          <t>Jun 29, 2026</t>
-        </is>
-      </c>
-      <c r="J64" s="37" t="inlineStr">
-        <is>
-          <t>19d</t>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>140P6026Q0025</t>
+        </is>
+      </c>
+      <c r="D64" s="30" t="inlineStr">
+        <is>
+          <t>FOSM - Replace Backflow Prevention Assemblies</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>Fort Smith, Arkansas</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I64" s="17" t="inlineStr">
+        <is>
+          <t>Jun 26, 2026</t>
+        </is>
+      </c>
+      <c r="J64" s="17" t="inlineStr">
+        <is>
+          <t>16d</t>
         </is>
       </c>
       <c r="K64" s="41" t="inlineStr">
@@ -5339,17 +5339,17 @@
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L64" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M64" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N64" s="40" t="inlineStr">
+      <c r="L64" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M64" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N64" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -5363,12 +5363,12 @@
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>89503426BWA000067</t>
+          <t>140R2026R0007</t>
         </is>
       </c>
       <c r="D65" s="33" t="inlineStr">
         <is>
-          <t>Denison Substation Stage 10, Iowa</t>
+          <t>CT SWITCHGEAR REPLACEMENT STAMPEDE PP</t>
         </is>
       </c>
       <c r="E65" s="20" t="inlineStr">
@@ -5378,112 +5378,112 @@
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="G65" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H65" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="20" t="inlineStr">
+        <is>
+          <t>Jun 27, 2026</t>
+        </is>
+      </c>
+      <c r="J65" s="20" t="inlineStr">
+        <is>
+          <t>17d</t>
+        </is>
+      </c>
+      <c r="K65" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L65" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="B66" s="36" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C66" s="37" t="inlineStr">
+        <is>
+          <t>W912QR26RA033</t>
+        </is>
+      </c>
+      <c r="D66" s="25" t="inlineStr">
+        <is>
+          <t>Anniston Army Depot (ANAD) Power Generation and Microgrid Project</t>
+        </is>
+      </c>
+      <c r="E66" s="37" t="inlineStr">
+        <is>
+          <t>Anniston, Alabama</t>
+        </is>
+      </c>
+      <c r="F66" s="37" t="inlineStr">
+        <is>
           <t>237130</t>
         </is>
       </c>
-      <c r="G65" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H65" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I65" s="20" t="inlineStr">
+      <c r="G66" s="38" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H66" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="37" t="inlineStr">
         <is>
           <t>Jun 29, 2026</t>
         </is>
       </c>
-      <c r="J65" s="20" t="inlineStr">
+      <c r="J66" s="37" t="inlineStr">
         <is>
           <t>19d</t>
         </is>
       </c>
-      <c r="K65" s="41" t="inlineStr">
+      <c r="K66" s="41" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L65" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M65" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N65" s="35" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="C66" s="17" t="inlineStr">
-        <is>
-          <t>140P6026B0005</t>
-        </is>
-      </c>
-      <c r="D66" s="30" t="inlineStr">
-        <is>
-          <t>Z--GRPO - Mile Creek Stone Trail Bridge</t>
-        </is>
-      </c>
-      <c r="E66" s="17" t="inlineStr">
-        <is>
-          <t>Grand Portage, Minnesota</t>
-        </is>
-      </c>
-      <c r="F66" s="17" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="G66" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H66" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I66" s="17" t="inlineStr">
-        <is>
-          <t>Jun 29, 2026</t>
-        </is>
-      </c>
-      <c r="J66" s="17" t="inlineStr">
-        <is>
-          <t>19d</t>
-        </is>
-      </c>
-      <c r="K66" s="41" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
-        </is>
-      </c>
-      <c r="L66" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M66" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N66" s="32" t="inlineStr">
+      <c r="L66" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M66" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N66" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -5497,12 +5497,12 @@
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>W912PM26BA001</t>
+          <t>89503426BWA000067</t>
         </is>
       </c>
       <c r="D67" s="33" t="inlineStr">
         <is>
-          <t>Atlantic Intracoastal Waterway (AIWW) Snows Cut Shoreline Erosion Bank Stabilization</t>
+          <t>Denison Substation Stage 10, Iowa</t>
         </is>
       </c>
       <c r="E67" s="20" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G67" s="20" t="inlineStr">
@@ -5564,127 +5564,127 @@
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>W9123826RA016</t>
+          <t>140P6026B0005</t>
         </is>
       </c>
       <c r="D68" s="30" t="inlineStr">
         <is>
-          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
+          <t>Z--GRPO - Mile Creek Stone Trail Bridge</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
+          <t>Grand Portage, Minnesota</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H68" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>Jun 29, 2026</t>
+        </is>
+      </c>
+      <c r="J68" s="17" t="inlineStr">
+        <is>
+          <t>19d</t>
+        </is>
+      </c>
+      <c r="K68" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L68" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="B69" s="20" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C69" s="20" t="inlineStr">
+        <is>
+          <t>W912PM26BA001</t>
+        </is>
+      </c>
+      <c r="D69" s="33" t="inlineStr">
+        <is>
+          <t>Atlantic Intracoastal Waterway (AIWW) Snows Cut Shoreline Erosion Bank Stabilization</t>
+        </is>
+      </c>
+      <c r="E69" s="20" t="inlineStr">
+        <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="F68" s="17" t="inlineStr">
-        <is>
-          <t>237130</t>
-        </is>
-      </c>
-      <c r="G68" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H68" s="17" t="inlineStr">
-        <is>
-          <t>$23.0M</t>
-        </is>
-      </c>
-      <c r="I68" s="17" t="inlineStr">
+      <c r="F69" s="20" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="G69" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H69" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="20" t="inlineStr">
         <is>
           <t>Jun 29, 2026</t>
         </is>
       </c>
-      <c r="J68" s="17" t="inlineStr">
+      <c r="J69" s="20" t="inlineStr">
         <is>
           <t>19d</t>
         </is>
       </c>
-      <c r="K68" s="41" t="inlineStr">
+      <c r="K69" s="41" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L68" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="B69" s="36" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C69" s="37" t="inlineStr">
-        <is>
-          <t>36C10F26B0001</t>
-        </is>
-      </c>
-      <c r="D69" s="25" t="inlineStr">
-        <is>
-          <t>Fort Sam Houston National Cemetery, Phase 3 Expansion - Additional Road Repairs</t>
-        </is>
-      </c>
-      <c r="E69" s="37" t="inlineStr">
-        <is>
-          <t>San Antonio, Texas</t>
-        </is>
-      </c>
-      <c r="F69" s="37" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="G69" s="38" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H69" s="37" t="inlineStr">
-        <is>
-          <t>$1.5M</t>
-        </is>
-      </c>
-      <c r="I69" s="37" t="inlineStr">
-        <is>
-          <t>Jun 30, 2026</t>
-        </is>
-      </c>
-      <c r="J69" s="37" t="inlineStr">
-        <is>
-          <t>20d</t>
-        </is>
-      </c>
-      <c r="K69" s="41" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
-        </is>
-      </c>
-      <c r="L69" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="40" t="inlineStr">
+      <c r="L69" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -5698,12 +5698,12 @@
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>W911WN26BA014</t>
+          <t>W9123826RA016</t>
         </is>
       </c>
       <c r="D70" s="30" t="inlineStr">
         <is>
-          <t>Shenango River Lake Water Tank Rehabiliation</t>
+          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G70" s="17" t="inlineStr">
@@ -5723,102 +5723,102 @@
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$23.0M</t>
         </is>
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
+          <t>Jun 29, 2026</t>
+        </is>
+      </c>
+      <c r="J70" s="17" t="inlineStr">
+        <is>
+          <t>19d</t>
+        </is>
+      </c>
+      <c r="K70" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L70" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="32" customHeight="1">
+      <c r="B71" s="36" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="C71" s="37" t="inlineStr">
+        <is>
+          <t>36C10F26B0001</t>
+        </is>
+      </c>
+      <c r="D71" s="25" t="inlineStr">
+        <is>
+          <t>Fort Sam Houston National Cemetery, Phase 3 Expansion - Additional Road Repairs</t>
+        </is>
+      </c>
+      <c r="E71" s="37" t="inlineStr">
+        <is>
+          <t>San Antonio, Texas</t>
+        </is>
+      </c>
+      <c r="F71" s="37" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="G71" s="38" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H71" s="37" t="inlineStr">
+        <is>
+          <t>$1.5M</t>
+        </is>
+      </c>
+      <c r="I71" s="37" t="inlineStr">
+        <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="J70" s="17" t="inlineStr">
+      <c r="J71" s="37" t="inlineStr">
         <is>
           <t>20d</t>
         </is>
       </c>
-      <c r="K70" s="41" t="inlineStr">
+      <c r="K71" s="41" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L70" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="32" customHeight="1">
-      <c r="B71" s="20" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="C71" s="20" t="inlineStr">
-        <is>
-          <t>12FPC326B0006</t>
-        </is>
-      </c>
-      <c r="D71" s="33" t="inlineStr">
-        <is>
-          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
-        </is>
-      </c>
-      <c r="E71" s="20" t="inlineStr">
-        <is>
-          <t>Madison, Ohio</t>
-        </is>
-      </c>
-      <c r="F71" s="20" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="G71" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H71" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="20" t="inlineStr">
-        <is>
-          <t>Jun 30, 2026</t>
-        </is>
-      </c>
-      <c r="J71" s="20" t="inlineStr">
-        <is>
-          <t>20d</t>
-        </is>
-      </c>
-      <c r="K71" s="41" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
-        </is>
-      </c>
-      <c r="L71" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="35" t="inlineStr">
+      <c r="L71" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -5832,22 +5832,22 @@
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>FA481426Q0026</t>
+          <t>W911WN26BA014</t>
         </is>
       </c>
       <c r="D72" s="30" t="inlineStr">
         <is>
-          <t>Electrical Upgrade for Brass Crusher</t>
+          <t>Shenango River Lake Water Tank Rehabiliation</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>Tampa, Florida</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G72" s="17" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="I72" s="17" t="inlineStr">
@@ -5899,22 +5899,22 @@
       </c>
       <c r="C73" s="20" t="inlineStr">
         <is>
-          <t>140P6026B0004</t>
+          <t>12FPC326B0006</t>
         </is>
       </c>
       <c r="D73" s="33" t="inlineStr">
         <is>
-          <t>Z--BRVB - Entry Courtyard Improvements</t>
+          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
         </is>
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
-          <t>Topeka, Kansas</t>
+          <t>Madison, Ohio</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G73" s="20" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="J73" s="20" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="K73" s="41" t="inlineStr">
@@ -5966,22 +5966,22 @@
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>140P8326Q0042</t>
+          <t>FA481426Q0026</t>
         </is>
       </c>
       <c r="D74" s="30" t="inlineStr">
         <is>
-          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
+          <t>Electrical Upgrade for Brass Crusher</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Tampa, Florida</t>
         </is>
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G74" s="17" t="inlineStr">
@@ -5991,17 +5991,17 @@
       </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>$11.4M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="J74" s="17" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="K74" s="41" t="inlineStr">
@@ -6033,22 +6033,22 @@
       </c>
       <c r="C75" s="20" t="inlineStr">
         <is>
-          <t>89503326BWA000019</t>
+          <t>140P6026B0004</t>
         </is>
       </c>
       <c r="D75" s="33" t="inlineStr">
         <is>
-          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
+          <t>Z--BRVB - Entry Courtyard Improvements</t>
         </is>
       </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Topeka, Kansas</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G75" s="20" t="inlineStr">
@@ -6063,12 +6063,12 @@
       </c>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>Jul 06, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="J75" s="20" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="K75" s="41" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0021</t>
+          <t>140P8326Q0042</t>
         </is>
       </c>
       <c r="D76" s="30" t="inlineStr">
         <is>
-          <t>Y--MI-SENEY NWR-DC DAM DECOMMISIONING</t>
+          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G76" s="17" t="inlineStr">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.4M</t>
         </is>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
-          <t>Jul 06, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="J76" s="17" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="K76" s="41" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="C77" s="20" t="inlineStr">
         <is>
-          <t>W9127N26BA015</t>
+          <t>89503326BWA000019</t>
         </is>
       </c>
       <c r="D77" s="33" t="inlineStr">
         <is>
-          <t>Oregon/Washington Clamshell Maintenance Dredging 2026</t>
+          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
         </is>
       </c>
       <c r="E77" s="20" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="F77" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G77" s="20" t="inlineStr">
@@ -6234,22 +6234,22 @@
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>140P8326Q0041</t>
+          <t>191BWC26B0001</t>
         </is>
       </c>
       <c r="D78" s="30" t="inlineStr">
         <is>
-          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
+          <t>Tainter Gates Sandblasting</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Del Rio, Texas</t>
         </is>
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G78" s="17" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="I78" s="17" t="inlineStr">
@@ -6301,17 +6301,17 @@
       </c>
       <c r="C79" s="20" t="inlineStr">
         <is>
-          <t>W9127826RA046</t>
+          <t>140FGA26R0021</t>
         </is>
       </c>
       <c r="D79" s="33" t="inlineStr">
         <is>
-          <t>Deer Island Ecosystem Restoration, Phase 1 Deer Island, MS (Harrison County)</t>
+          <t>Y--MI-SENEY NWR-DC DAM DECOMMISIONING</t>
         </is>
       </c>
       <c r="E79" s="20" t="inlineStr">
         <is>
-          <t>Biloxi, Mississippi</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F79" s="20" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="J79" s="20" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="K79" s="41" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>W912P926BA007</t>
+          <t>W9127N26BA015</t>
         </is>
       </c>
       <c r="D80" s="30" t="inlineStr">
         <is>
-          <t>Crains Island Stage 3</t>
+          <t>Oregon/Washington Clamshell Maintenance Dredging 2026</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="I80" s="17" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="J80" s="17" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="K80" s="41" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="C81" s="20" t="inlineStr">
         <is>
-          <t>140P5326R0006</t>
+          <t>140P8326Q0041</t>
         </is>
       </c>
       <c r="D81" s="33" t="inlineStr">
         <is>
-          <t>MACA-REHAB ENTRANCE SIGNS/PARKING AREAS</t>
+          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
         </is>
       </c>
       <c r="E81" s="20" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="F81" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G81" s="20" t="inlineStr">
@@ -6465,12 +6465,12 @@
       </c>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>Jul 08, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="J81" s="20" t="inlineStr">
         <is>
-          <t>28d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="K81" s="41" t="inlineStr">
@@ -6502,17 +6502,17 @@
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>140P6426B0008</t>
+          <t>W9127826RA046</t>
         </is>
       </c>
       <c r="D82" s="30" t="inlineStr">
         <is>
-          <t>Z--ZION- Crawford Dam Removal and Diversion</t>
+          <t>Deer Island Ecosystem Restoration, Phase 1 Deer Island, MS (Harrison County)</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Biloxi, Mississippi</t>
         </is>
       </c>
       <c r="F82" s="17" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I82" s="17" t="inlineStr">
         <is>
-          <t>Jul 08, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="J82" s="17" t="inlineStr">
         <is>
-          <t>28d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="K82" s="41" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="C83" s="20" t="inlineStr">
         <is>
-          <t>N6247326R9953</t>
+          <t>W912P926BA007</t>
         </is>
       </c>
       <c r="D83" s="33" t="inlineStr">
         <is>
-          <t>Base Operations Support Contract (BOSC) for Naval Air Weapons Station (NAWS) China Lake, California and Other Locations as Approved</t>
+          <t>Crains Island Stage 3</t>
         </is>
       </c>
       <c r="E83" s="20" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="F83" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G83" s="20" t="inlineStr">
@@ -6594,17 +6594,17 @@
       </c>
       <c r="H83" s="20" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="J83" s="20" t="inlineStr">
         <is>
-          <t>30d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="K83" s="41" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>140R4026R0010</t>
+          <t>FA282326R0014</t>
         </is>
       </c>
       <c r="D84" s="30" t="inlineStr">
         <is>
-          <t>J--GC26 FIRE ALARM SYSTEM REPLACEMENT</t>
+          <t xml:space="preserve">RELOCATABLE FACILITY (RFL) MAINTENANCE AND REPAIR SERVICES - EGLIN AFB </t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="G84" s="17" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="J84" s="17" t="inlineStr">
         <is>
-          <t>30d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="K84" s="41" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="C85" s="20" t="inlineStr">
         <is>
-          <t>N6247326R0053</t>
+          <t>140P5326R0006</t>
         </is>
       </c>
       <c r="D85" s="33" t="inlineStr">
         <is>
-          <t>CHINA LAKE BOSC - SOLICITATION - N6247326R0053</t>
+          <t>MACA-REHAB ENTRANCE SIGNS/PARKING AREAS</t>
         </is>
       </c>
       <c r="E85" s="20" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="F85" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G85" s="20" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 08, 2026</t>
         </is>
       </c>
       <c r="J85" s="20" t="inlineStr">
         <is>
-          <t>30d</t>
+          <t>28d</t>
         </is>
       </c>
       <c r="K85" s="41" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>W9128F26RA056</t>
+          <t>140P6426B0008</t>
         </is>
       </c>
       <c r="D86" s="30" t="inlineStr">
         <is>
-          <t>Solicitation for Grand Forks Fueling System Repairs</t>
+          <t>Z--ZION- Crawford Dam Removal and Diversion</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>237120</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G86" s="17" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 08, 2026</t>
         </is>
       </c>
       <c r="J86" s="17" t="inlineStr">
         <is>
-          <t>30d</t>
+          <t>28d</t>
         </is>
       </c>
       <c r="K86" s="41" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="C87" s="20" t="inlineStr">
         <is>
-          <t>140L3626Q0032</t>
+          <t>N6247326R9953</t>
         </is>
       </c>
       <c r="D87" s="33" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>Base Operations Support Contract (BOSC) for Naval Air Weapons Station (NAWS) China Lake, California and Other Locations as Approved</t>
         </is>
       </c>
       <c r="E87" s="20" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="F87" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="G87" s="20" t="inlineStr">
@@ -6862,22 +6862,22 @@
       </c>
       <c r="H87" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$47.0M</t>
         </is>
       </c>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 10, 2026</t>
         </is>
       </c>
       <c r="J87" s="20" t="inlineStr">
         <is>
-          <t>35d</t>
-        </is>
-      </c>
-      <c r="K87" s="42" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+          <t>30d</t>
+        </is>
+      </c>
+      <c r="K87" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="L87" s="20" t="inlineStr">
@@ -6897,67 +6897,67 @@
       </c>
     </row>
     <row r="88" ht="32" customHeight="1">
-      <c r="B88" s="36" t="inlineStr">
+      <c r="B88" s="17" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="C88" s="37" t="inlineStr">
-        <is>
-          <t>36C25626R0015</t>
-        </is>
-      </c>
-      <c r="D88" s="25" t="inlineStr">
-        <is>
-          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
-        </is>
-      </c>
-      <c r="E88" s="37" t="inlineStr">
-        <is>
-          <t>Fayetteville, Arkansas</t>
-        </is>
-      </c>
-      <c r="F88" s="37" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="G88" s="38" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H88" s="37" t="inlineStr">
-        <is>
-          <t>$15.0M</t>
-        </is>
-      </c>
-      <c r="I88" s="37" t="inlineStr">
-        <is>
-          <t>Jul 23, 2026</t>
-        </is>
-      </c>
-      <c r="J88" s="37" t="inlineStr">
-        <is>
-          <t>43d</t>
-        </is>
-      </c>
-      <c r="K88" s="42" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
-        </is>
-      </c>
-      <c r="L88" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M88" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N88" s="40" t="inlineStr">
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>140R4026R0010</t>
+        </is>
+      </c>
+      <c r="D88" s="30" t="inlineStr">
+        <is>
+          <t>J--GC26 FIRE ALARM SYSTEM REPLACEMENT</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>Jul 10, 2026</t>
+        </is>
+      </c>
+      <c r="J88" s="17" t="inlineStr">
+        <is>
+          <t>30d</t>
+        </is>
+      </c>
+      <c r="K88" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L88" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M88" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N88" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -6971,67 +6971,335 @@
       </c>
       <c r="C89" s="20" t="inlineStr">
         <is>
+          <t>N6247326R0053</t>
+        </is>
+      </c>
+      <c r="D89" s="33" t="inlineStr">
+        <is>
+          <t>CHINA LAKE BOSC - SOLICITATION - N6247326R0053</t>
+        </is>
+      </c>
+      <c r="E89" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F89" s="20" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="G89" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H89" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" s="20" t="inlineStr">
+        <is>
+          <t>Jul 10, 2026</t>
+        </is>
+      </c>
+      <c r="J89" s="20" t="inlineStr">
+        <is>
+          <t>30d</t>
+        </is>
+      </c>
+      <c r="K89" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L89" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M89" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N89" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="32" customHeight="1">
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
+        <is>
+          <t>W9128F26RA056</t>
+        </is>
+      </c>
+      <c r="D90" s="30" t="inlineStr">
+        <is>
+          <t>Solicitation for Grand Forks Fueling System Repairs</t>
+        </is>
+      </c>
+      <c r="E90" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>237120</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H90" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>Jul 10, 2026</t>
+        </is>
+      </c>
+      <c r="J90" s="17" t="inlineStr">
+        <is>
+          <t>30d</t>
+        </is>
+      </c>
+      <c r="K90" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L90" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M90" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N90" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="B91" s="20" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="C91" s="20" t="inlineStr">
+        <is>
+          <t>140L3626Q0032</t>
+        </is>
+      </c>
+      <c r="D91" s="33" t="inlineStr">
+        <is>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+        </is>
+      </c>
+      <c r="E91" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F91" s="20" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="G91" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H91" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="20" t="inlineStr">
+        <is>
+          <t>Jul 15, 2026</t>
+        </is>
+      </c>
+      <c r="J91" s="20" t="inlineStr">
+        <is>
+          <t>35d</t>
+        </is>
+      </c>
+      <c r="K91" s="42" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
+        </is>
+      </c>
+      <c r="L91" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M91" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N91" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="32" customHeight="1">
+      <c r="B92" s="36" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C92" s="37" t="inlineStr">
+        <is>
+          <t>36C25626R0015</t>
+        </is>
+      </c>
+      <c r="D92" s="25" t="inlineStr">
+        <is>
+          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
+        </is>
+      </c>
+      <c r="E92" s="37" t="inlineStr">
+        <is>
+          <t>Fayetteville, Arkansas</t>
+        </is>
+      </c>
+      <c r="F92" s="37" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="G92" s="38" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H92" s="37" t="inlineStr">
+        <is>
+          <t>$15.0M</t>
+        </is>
+      </c>
+      <c r="I92" s="37" t="inlineStr">
+        <is>
+          <t>Jul 23, 2026</t>
+        </is>
+      </c>
+      <c r="J92" s="37" t="inlineStr">
+        <is>
+          <t>43d</t>
+        </is>
+      </c>
+      <c r="K92" s="42" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
+        </is>
+      </c>
+      <c r="L92" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M92" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N92" s="40" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="32" customHeight="1">
+      <c r="B93" s="20" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C93" s="20" t="inlineStr">
+        <is>
           <t>140P6026Q0042</t>
         </is>
       </c>
-      <c r="D89" s="33" t="inlineStr">
+      <c r="D93" s="33" t="inlineStr">
         <is>
           <t>Z--FOLS, Replace Alarm System &amp; Electrical Panel</t>
         </is>
       </c>
-      <c r="E89" s="20" t="inlineStr">
+      <c r="E93" s="20" t="inlineStr">
         <is>
           <t>Larned, Kansas</t>
         </is>
       </c>
-      <c r="F89" s="20" t="inlineStr">
+      <c r="F93" s="20" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="G89" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H89" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I89" s="20" t="inlineStr">
+      <c r="G93" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H93" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" s="20" t="inlineStr">
         <is>
           <t>Jun 10, 2026</t>
         </is>
       </c>
-      <c r="J89" s="20" t="inlineStr">
+      <c r="J93" s="20" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="K89" s="18" t="inlineStr">
+      <c r="K93" s="18" t="inlineStr">
         <is>
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L89" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M89" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N89" s="35" t="inlineStr">
+      <c r="L93" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M93" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N93" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:N89"/>
+  <autoFilter ref="B5:N93"/>
   <mergeCells count="2">
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="B2:N2"/>
@@ -7121,6 +7389,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N87" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N88" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N89" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N90" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N91" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N92" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N93" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7133,7 +7405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K50"/>
+  <dimension ref="B2:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7161,7 +7433,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>Early-stage opportunities to monitor  ·  45 records  (6 SDVOSB)  ·  SDVOSB first, then AI score desc</t>
+          <t>Early-stage opportunities to monitor  ·  46 records  (6 SDVOSB)  ·  SDVOSB first, then AI score desc</t>
         </is>
       </c>
     </row>
@@ -9558,8 +9830,60 @@
         </is>
       </c>
     </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>140P5426R0017</t>
+        </is>
+      </c>
+      <c r="C51" s="33" t="inlineStr">
+        <is>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="20" t="inlineStr">
+        <is>
+          <t>Jul 24, 2026</t>
+        </is>
+      </c>
+      <c r="I51" s="20" t="inlineStr">
+        <is>
+          <t>44d</t>
+        </is>
+      </c>
+      <c r="J51" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K51" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B5:K50"/>
+  <autoFilter ref="B5:K51"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -9575,7 +9899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K134"/>
+  <dimension ref="B2:K139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -9603,7 +9927,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>Complete data  ·  129 records  ·  June 09, 2026</t>
+          <t>Complete data  ·  134 records  ·  June 09, 2026</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11656,7 @@
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>PAIS WASTE WATER TANK REPLACEMENT</t>
+          <t>Y--PAIS WASTE WATER TANK REPLACEMENT</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
@@ -12003,12 +12327,12 @@
     <row r="51" ht="28" customHeight="1">
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>140P9726R0002</t>
+          <t>140FS226Q0120</t>
         </is>
       </c>
       <c r="C51" s="33" t="inlineStr">
         <is>
-          <t>Y--GLBA REHAB WATERLINE</t>
+          <t>NM - SW NATIVE ARC - 5-Year BPA for Well Repair</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -12033,12 +12357,12 @@
       </c>
       <c r="H51" s="20" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="I51" s="20" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>13d</t>
         </is>
       </c>
       <c r="J51" s="20" t="inlineStr">
@@ -12055,12 +12379,12 @@
     <row r="52" ht="28" customHeight="1">
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>W50S8526BA001</t>
+          <t>140FC126R0025</t>
         </is>
       </c>
       <c r="C52" s="30" t="inlineStr">
         <is>
-          <t>VGLZ 182035 REPAIR BASE PERIMETER ROAD</t>
+          <t>Y--Hasty Point Rice Trunk &amp;</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -12070,7 +12394,7 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F52" s="17" t="inlineStr">
@@ -12085,12 +12409,12 @@
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>13d</t>
         </is>
       </c>
       <c r="J52" s="17" t="inlineStr">
@@ -12107,12 +12431,12 @@
     <row r="53" ht="28" customHeight="1">
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>140FC326Q0025</t>
+          <t>140P9726R0002</t>
         </is>
       </c>
       <c r="C53" s="33" t="inlineStr">
         <is>
-          <t>NM DEXTER NFHTC POND LINER 12B &amp; 13B</t>
+          <t>Y--GLBA REHAB WATERLINE</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
@@ -12122,7 +12446,7 @@
       </c>
       <c r="E53" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F53" s="20" t="inlineStr">
@@ -12159,12 +12483,12 @@
     <row r="54" ht="28" customHeight="1">
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>140P9726Q0044</t>
+          <t>W50S8526BA001</t>
         </is>
       </c>
       <c r="C54" s="30" t="inlineStr">
         <is>
-          <t>EO14398 UST ASSESSMENT &amp; REPORTING - GLBA</t>
+          <t>VGLZ 182035 REPAIR BASE PERIMETER ROAD</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -12174,7 +12498,7 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>213112</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F54" s="17" t="inlineStr">
@@ -12211,12 +12535,12 @@
     <row r="55" ht="28" customHeight="1">
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>140P6426Q0073</t>
+          <t>140FC326Q0025</t>
         </is>
       </c>
       <c r="C55" s="33" t="inlineStr">
         <is>
-          <t>Crack and Fog Sealing Multiple Locations</t>
+          <t>NM DEXTER NFHTC POND LINER 12B &amp; 13B</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
@@ -12226,7 +12550,7 @@
       </c>
       <c r="E55" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F55" s="20" t="inlineStr">
@@ -12236,17 +12560,17 @@
       </c>
       <c r="G55" s="20" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H55" s="20" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Jun 24, 2026</t>
         </is>
       </c>
       <c r="I55" s="20" t="inlineStr">
         <is>
-          <t>15d</t>
+          <t>14d</t>
         </is>
       </c>
       <c r="J55" s="20" t="inlineStr">
@@ -12261,52 +12585,52 @@
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
-      <c r="B56" s="37" t="inlineStr">
-        <is>
-          <t>W9128F26RA063</t>
-        </is>
-      </c>
-      <c r="C56" s="25" t="inlineStr">
-        <is>
-          <t>Fort Riley Tank CoatingsRepair</t>
-        </is>
-      </c>
-      <c r="D56" s="37" t="inlineStr">
-        <is>
-          <t>Fort Riley, Kansas</t>
-        </is>
-      </c>
-      <c r="E56" s="37" t="inlineStr">
-        <is>
-          <t>237120</t>
-        </is>
-      </c>
-      <c r="F56" s="37" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G56" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="37" t="inlineStr">
-        <is>
-          <t>Jun 25, 2026</t>
-        </is>
-      </c>
-      <c r="I56" s="37" t="inlineStr">
-        <is>
-          <t>15d</t>
-        </is>
-      </c>
-      <c r="J56" s="37" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>140P9726Q0044</t>
+        </is>
+      </c>
+      <c r="C56" s="30" t="inlineStr">
+        <is>
+          <t>EO14398 UST ASSESSMENT &amp; REPORTING - GLBA</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>213112</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
+        <is>
+          <t>14d</t>
+        </is>
+      </c>
+      <c r="J56" s="17" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K56" s="40" t="inlineStr">
+      <c r="K56" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -12315,12 +12639,12 @@
     <row r="57" ht="28" customHeight="1">
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>W911KB26RA039</t>
+          <t>140P6426Q0073</t>
         </is>
       </c>
       <c r="C57" s="33" t="inlineStr">
         <is>
-          <t>FTW506 Life Safety Repairs</t>
+          <t>Crack and Fog Sealing Multiple Locations</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
@@ -12330,7 +12654,7 @@
       </c>
       <c r="E57" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F57" s="20" t="inlineStr">
@@ -12340,7 +12664,7 @@
       </c>
       <c r="G57" s="20" t="inlineStr">
         <is>
-          <t>$18.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="H57" s="20" t="inlineStr">
@@ -12365,52 +12689,52 @@
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>W9124D26QA266</t>
-        </is>
-      </c>
-      <c r="C58" s="30" t="inlineStr">
-        <is>
-          <t>USMEPCOM Low Voltage Cable Removal</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="inlineStr">
-        <is>
-          <t>North Chicago, Illinois</t>
-        </is>
-      </c>
-      <c r="E58" s="17" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F58" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G58" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="17" t="inlineStr">
+      <c r="B58" s="37" t="inlineStr">
+        <is>
+          <t>W9128F26RA063</t>
+        </is>
+      </c>
+      <c r="C58" s="25" t="inlineStr">
+        <is>
+          <t>Fort Riley Tank CoatingsRepair</t>
+        </is>
+      </c>
+      <c r="D58" s="37" t="inlineStr">
+        <is>
+          <t>Fort Riley, Kansas</t>
+        </is>
+      </c>
+      <c r="E58" s="37" t="inlineStr">
+        <is>
+          <t>237120</t>
+        </is>
+      </c>
+      <c r="F58" s="37" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G58" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="37" t="inlineStr">
         <is>
           <t>Jun 25, 2026</t>
         </is>
       </c>
-      <c r="I58" s="17" t="inlineStr">
+      <c r="I58" s="37" t="inlineStr">
         <is>
           <t>15d</t>
         </is>
       </c>
-      <c r="J58" s="17" t="inlineStr">
+      <c r="J58" s="37" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K58" s="32" t="inlineStr">
+      <c r="K58" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -12419,22 +12743,22 @@
     <row r="59" ht="28" customHeight="1">
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>1605AE-26-Q-00005</t>
+          <t>W911KB26RA039</t>
         </is>
       </c>
       <c r="C59" s="33" t="inlineStr">
         <is>
-          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
+          <t>FTW506 Life Safety Repairs</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F59" s="20" t="inlineStr">
@@ -12444,7 +12768,7 @@
       </c>
       <c r="G59" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$18.0M</t>
         </is>
       </c>
       <c r="H59" s="20" t="inlineStr">
@@ -12471,22 +12795,22 @@
     <row r="60" ht="28" customHeight="1">
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0010</t>
+          <t>W9124D26QA266</t>
         </is>
       </c>
       <c r="C60" s="30" t="inlineStr">
         <is>
-          <t>Y--FOMA REPLACE NATURE TRAIL BOARDWALK RS</t>
+          <t>USMEPCOM Low Voltage Cable Removal</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>North Chicago, Illinois</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F60" s="17" t="inlineStr">
@@ -12501,12 +12825,12 @@
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>Jun 26, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>16d</t>
+          <t>15d</t>
         </is>
       </c>
       <c r="J60" s="17" t="inlineStr">
@@ -12523,22 +12847,22 @@
     <row r="61" ht="28" customHeight="1">
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>89503426BWA000066</t>
+          <t>1605AE-26-Q-00005</t>
         </is>
       </c>
       <c r="C61" s="33" t="inlineStr">
         <is>
-          <t>Carpenter Substation Stage 03 South Dakota</t>
+          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Atlanta, Georgia</t>
         </is>
       </c>
       <c r="E61" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F61" s="20" t="inlineStr">
@@ -12553,12 +12877,12 @@
       </c>
       <c r="H61" s="20" t="inlineStr">
         <is>
-          <t>Jun 26, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="I61" s="20" t="inlineStr">
         <is>
-          <t>16d</t>
+          <t>15d</t>
         </is>
       </c>
       <c r="J61" s="20" t="inlineStr">
@@ -12575,22 +12899,22 @@
     <row r="62" ht="28" customHeight="1">
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>140P6026Q0025</t>
+          <t>140P5426R0010</t>
         </is>
       </c>
       <c r="C62" s="30" t="inlineStr">
         <is>
-          <t>FOSM - Replace Backflow Prevention Assemblies</t>
+          <t>Y--FOMA REPLACE NATURE TRAIL BOARDWALK RS</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>Fort Smith, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F62" s="17" t="inlineStr">
@@ -12627,12 +12951,12 @@
     <row r="63" ht="28" customHeight="1">
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>140R2026R0007</t>
+          <t>89503426BWA000066</t>
         </is>
       </c>
       <c r="C63" s="33" t="inlineStr">
         <is>
-          <t>CT SWITCHGEAR REPLACEMENT STAMPEDE PP</t>
+          <t>Carpenter Substation Stage 03 South Dakota</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -12642,7 +12966,7 @@
       </c>
       <c r="E63" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F63" s="20" t="inlineStr">
@@ -12657,12 +12981,12 @@
       </c>
       <c r="H63" s="20" t="inlineStr">
         <is>
-          <t>Jun 27, 2026</t>
+          <t>Jun 26, 2026</t>
         </is>
       </c>
       <c r="I63" s="20" t="inlineStr">
         <is>
-          <t>17d</t>
+          <t>16d</t>
         </is>
       </c>
       <c r="J63" s="20" t="inlineStr">
@@ -12677,52 +13001,52 @@
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
-      <c r="B64" s="37" t="inlineStr">
-        <is>
-          <t>W912QR26RA033</t>
-        </is>
-      </c>
-      <c r="C64" s="25" t="inlineStr">
-        <is>
-          <t>Anniston Army Depot (ANAD) Power Generation and Microgrid Project</t>
-        </is>
-      </c>
-      <c r="D64" s="37" t="inlineStr">
-        <is>
-          <t>Anniston, Alabama</t>
-        </is>
-      </c>
-      <c r="E64" s="37" t="inlineStr">
-        <is>
-          <t>237130</t>
-        </is>
-      </c>
-      <c r="F64" s="37" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G64" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H64" s="37" t="inlineStr">
-        <is>
-          <t>Jun 29, 2026</t>
-        </is>
-      </c>
-      <c r="I64" s="37" t="inlineStr">
-        <is>
-          <t>19d</t>
-        </is>
-      </c>
-      <c r="J64" s="37" t="inlineStr">
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>140P6026Q0025</t>
+        </is>
+      </c>
+      <c r="C64" s="30" t="inlineStr">
+        <is>
+          <t>FOSM - Replace Backflow Prevention Assemblies</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>Fort Smith, Arkansas</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
+          <t>Jun 26, 2026</t>
+        </is>
+      </c>
+      <c r="I64" s="17" t="inlineStr">
+        <is>
+          <t>16d</t>
+        </is>
+      </c>
+      <c r="J64" s="17" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K64" s="40" t="inlineStr">
+      <c r="K64" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -12731,12 +13055,12 @@
     <row r="65" ht="28" customHeight="1">
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>89503426BWA000067</t>
+          <t>140R2026R0007</t>
         </is>
       </c>
       <c r="C65" s="33" t="inlineStr">
         <is>
-          <t>Denison Substation Stage 10, Iowa</t>
+          <t>CT SWITCHGEAR REPLACEMENT STAMPEDE PP</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -12746,87 +13070,87 @@
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F65" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G65" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="20" t="inlineStr">
+        <is>
+          <t>Jun 27, 2026</t>
+        </is>
+      </c>
+      <c r="I65" s="20" t="inlineStr">
+        <is>
+          <t>17d</t>
+        </is>
+      </c>
+      <c r="J65" s="20" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K65" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="B66" s="37" t="inlineStr">
+        <is>
+          <t>W912QR26RA033</t>
+        </is>
+      </c>
+      <c r="C66" s="25" t="inlineStr">
+        <is>
+          <t>Anniston Army Depot (ANAD) Power Generation and Microgrid Project</t>
+        </is>
+      </c>
+      <c r="D66" s="37" t="inlineStr">
+        <is>
+          <t>Anniston, Alabama</t>
+        </is>
+      </c>
+      <c r="E66" s="37" t="inlineStr">
+        <is>
           <t>237130</t>
         </is>
       </c>
-      <c r="F65" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G65" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H65" s="20" t="inlineStr">
+      <c r="F66" s="37" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G66" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="37" t="inlineStr">
         <is>
           <t>Jun 29, 2026</t>
         </is>
       </c>
-      <c r="I65" s="20" t="inlineStr">
+      <c r="I66" s="37" t="inlineStr">
         <is>
           <t>19d</t>
         </is>
       </c>
-      <c r="J65" s="20" t="inlineStr">
+      <c r="J66" s="37" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K65" s="35" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t>140P6026B0005</t>
-        </is>
-      </c>
-      <c r="C66" s="30" t="inlineStr">
-        <is>
-          <t>Z--GRPO - Mile Creek Stone Trail Bridge</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="inlineStr">
-        <is>
-          <t>Grand Portage, Minnesota</t>
-        </is>
-      </c>
-      <c r="E66" s="17" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F66" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G66" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H66" s="17" t="inlineStr">
-        <is>
-          <t>Jun 29, 2026</t>
-        </is>
-      </c>
-      <c r="I66" s="17" t="inlineStr">
-        <is>
-          <t>19d</t>
-        </is>
-      </c>
-      <c r="J66" s="17" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="inlineStr">
+      <c r="K66" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -12835,12 +13159,12 @@
     <row r="67" ht="28" customHeight="1">
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>W912PM26BA001</t>
+          <t>89503426BWA000067</t>
         </is>
       </c>
       <c r="C67" s="33" t="inlineStr">
         <is>
-          <t>Atlantic Intracoastal Waterway (AIWW) Snows Cut Shoreline Erosion Bank Stabilization</t>
+          <t>Denison Substation Stage 10, Iowa</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -12850,7 +13174,7 @@
       </c>
       <c r="E67" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F67" s="20" t="inlineStr">
@@ -12887,102 +13211,102 @@
     <row r="68" ht="28" customHeight="1">
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>W9123826RA016</t>
+          <t>140P6026B0005</t>
         </is>
       </c>
       <c r="C68" s="30" t="inlineStr">
         <is>
-          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
+          <t>Z--GRPO - Mile Creek Stone Trail Bridge</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
+          <t>Grand Portage, Minnesota</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="17" t="inlineStr">
+        <is>
+          <t>Jun 29, 2026</t>
+        </is>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>19d</t>
+        </is>
+      </c>
+      <c r="J68" s="17" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="B69" s="20" t="inlineStr">
+        <is>
+          <t>W912PM26BA001</t>
+        </is>
+      </c>
+      <c r="C69" s="33" t="inlineStr">
+        <is>
+          <t>Atlantic Intracoastal Waterway (AIWW) Snows Cut Shoreline Erosion Bank Stabilization</t>
+        </is>
+      </c>
+      <c r="D69" s="20" t="inlineStr">
+        <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E68" s="17" t="inlineStr">
-        <is>
-          <t>237130</t>
-        </is>
-      </c>
-      <c r="F68" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G68" s="17" t="inlineStr">
-        <is>
-          <t>$23.0M</t>
-        </is>
-      </c>
-      <c r="H68" s="17" t="inlineStr">
+      <c r="E69" s="20" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F69" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G69" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="20" t="inlineStr">
         <is>
           <t>Jun 29, 2026</t>
         </is>
       </c>
-      <c r="I68" s="17" t="inlineStr">
+      <c r="I69" s="20" t="inlineStr">
         <is>
           <t>19d</t>
         </is>
       </c>
-      <c r="J68" s="17" t="inlineStr">
+      <c r="J69" s="20" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="B69" s="37" t="inlineStr">
-        <is>
-          <t>36C10F26B0001</t>
-        </is>
-      </c>
-      <c r="C69" s="25" t="inlineStr">
-        <is>
-          <t>Fort Sam Houston National Cemetery, Phase 3 Expansion - Additional Road Repairs</t>
-        </is>
-      </c>
-      <c r="D69" s="37" t="inlineStr">
-        <is>
-          <t>San Antonio, Texas</t>
-        </is>
-      </c>
-      <c r="E69" s="37" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F69" s="37" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G69" s="37" t="inlineStr">
-        <is>
-          <t>$1.5M</t>
-        </is>
-      </c>
-      <c r="H69" s="37" t="inlineStr">
-        <is>
-          <t>Jun 30, 2026</t>
-        </is>
-      </c>
-      <c r="I69" s="37" t="inlineStr">
-        <is>
-          <t>20d</t>
-        </is>
-      </c>
-      <c r="J69" s="37" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K69" s="40" t="inlineStr">
+      <c r="K69" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -12991,12 +13315,12 @@
     <row r="70" ht="28" customHeight="1">
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>W911WN26BA014</t>
+          <t>W9123826RA016</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>Shenango River Lake Water Tank Rehabiliation</t>
+          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
@@ -13006,7 +13330,7 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F70" s="17" t="inlineStr">
@@ -13016,77 +13340,77 @@
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$23.0M</t>
         </is>
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
+          <t>Jun 29, 2026</t>
+        </is>
+      </c>
+      <c r="I70" s="17" t="inlineStr">
+        <is>
+          <t>19d</t>
+        </is>
+      </c>
+      <c r="J70" s="17" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="B71" s="37" t="inlineStr">
+        <is>
+          <t>36C10F26B0001</t>
+        </is>
+      </c>
+      <c r="C71" s="25" t="inlineStr">
+        <is>
+          <t>Fort Sam Houston National Cemetery, Phase 3 Expansion - Additional Road Repairs</t>
+        </is>
+      </c>
+      <c r="D71" s="37" t="inlineStr">
+        <is>
+          <t>San Antonio, Texas</t>
+        </is>
+      </c>
+      <c r="E71" s="37" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F71" s="37" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G71" s="37" t="inlineStr">
+        <is>
+          <t>$1.5M</t>
+        </is>
+      </c>
+      <c r="H71" s="37" t="inlineStr">
+        <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="I70" s="17" t="inlineStr">
+      <c r="I71" s="37" t="inlineStr">
         <is>
           <t>20d</t>
         </is>
       </c>
-      <c r="J70" s="17" t="inlineStr">
+      <c r="J71" s="37" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="28" customHeight="1">
-      <c r="B71" s="20" t="inlineStr">
-        <is>
-          <t>12FPC326B0006</t>
-        </is>
-      </c>
-      <c r="C71" s="33" t="inlineStr">
-        <is>
-          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
-        </is>
-      </c>
-      <c r="D71" s="20" t="inlineStr">
-        <is>
-          <t>Madison, Ohio</t>
-        </is>
-      </c>
-      <c r="E71" s="20" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F71" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G71" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="20" t="inlineStr">
-        <is>
-          <t>Jun 30, 2026</t>
-        </is>
-      </c>
-      <c r="I71" s="20" t="inlineStr">
-        <is>
-          <t>20d</t>
-        </is>
-      </c>
-      <c r="J71" s="20" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K71" s="35" t="inlineStr">
+      <c r="K71" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -13095,22 +13419,22 @@
     <row r="72" ht="28" customHeight="1">
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>FA481426Q0026</t>
+          <t>W911WN26BA014</t>
         </is>
       </c>
       <c r="C72" s="30" t="inlineStr">
         <is>
-          <t>Electrical Upgrade for Brass Crusher</t>
+          <t>Shenango River Lake Water Tank Rehabiliation</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t>Tampa, Florida</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F72" s="17" t="inlineStr">
@@ -13120,7 +13444,7 @@
       </c>
       <c r="G72" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="H72" s="17" t="inlineStr">
@@ -13147,22 +13471,22 @@
     <row r="73" ht="28" customHeight="1">
       <c r="B73" s="20" t="inlineStr">
         <is>
-          <t>140P6026B0004</t>
+          <t>12FPC326B0006</t>
         </is>
       </c>
       <c r="C73" s="33" t="inlineStr">
         <is>
-          <t>Z--BRVB - Entry Courtyard Improvements</t>
+          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
         <is>
-          <t>Topeka, Kansas</t>
+          <t>Madison, Ohio</t>
         </is>
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
@@ -13177,12 +13501,12 @@
       </c>
       <c r="H73" s="20" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="J73" s="20" t="inlineStr">
@@ -13199,22 +13523,22 @@
     <row r="74" ht="28" customHeight="1">
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>140P8326Q0042</t>
+          <t>FA481426Q0026</t>
         </is>
       </c>
       <c r="C74" s="30" t="inlineStr">
         <is>
-          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
+          <t>Electrical Upgrade for Brass Crusher</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Tampa, Florida</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F74" s="17" t="inlineStr">
@@ -13224,17 +13548,17 @@
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>$11.4M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="J74" s="17" t="inlineStr">
@@ -13251,22 +13575,22 @@
     <row r="75" ht="28" customHeight="1">
       <c r="B75" s="20" t="inlineStr">
         <is>
-          <t>89503326BWA000019</t>
+          <t>140P6026B0004</t>
         </is>
       </c>
       <c r="C75" s="33" t="inlineStr">
         <is>
-          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
+          <t>Z--BRVB - Entry Courtyard Improvements</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Topeka, Kansas</t>
         </is>
       </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
@@ -13281,12 +13605,12 @@
       </c>
       <c r="H75" s="20" t="inlineStr">
         <is>
-          <t>Jul 06, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="J75" s="20" t="inlineStr">
@@ -13303,12 +13627,12 @@
     <row r="76" ht="28" customHeight="1">
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0021</t>
+          <t>140P8326Q0042</t>
         </is>
       </c>
       <c r="C76" s="30" t="inlineStr">
         <is>
-          <t>Y--MI-SENEY NWR-DC DAM DECOMMISIONING</t>
+          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
         </is>
       </c>
       <c r="D76" s="17" t="inlineStr">
@@ -13318,7 +13642,7 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F76" s="17" t="inlineStr">
@@ -13328,17 +13652,17 @@
       </c>
       <c r="G76" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.4M</t>
         </is>
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>Jul 06, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="J76" s="17" t="inlineStr">
@@ -13355,12 +13679,12 @@
     <row r="77" ht="28" customHeight="1">
       <c r="B77" s="20" t="inlineStr">
         <is>
-          <t>W9127N26BA015</t>
+          <t>89503326BWA000019</t>
         </is>
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
-          <t>Oregon/Washington Clamshell Maintenance Dredging 2026</t>
+          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -13370,7 +13694,7 @@
       </c>
       <c r="E77" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
@@ -13407,22 +13731,22 @@
     <row r="78" ht="28" customHeight="1">
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>140P8326Q0041</t>
+          <t>191BWC26B0001</t>
         </is>
       </c>
       <c r="C78" s="30" t="inlineStr">
         <is>
-          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
+          <t>Tainter Gates Sandblasting</t>
         </is>
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Del Rio, Texas</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F78" s="17" t="inlineStr">
@@ -13432,7 +13756,7 @@
       </c>
       <c r="G78" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H78" s="17" t="inlineStr">
@@ -13459,17 +13783,17 @@
     <row r="79" ht="28" customHeight="1">
       <c r="B79" s="20" t="inlineStr">
         <is>
-          <t>W9127826RA046</t>
+          <t>140FGA26R0021</t>
         </is>
       </c>
       <c r="C79" s="33" t="inlineStr">
         <is>
-          <t>Deer Island Ecosystem Restoration, Phase 1 Deer Island, MS (Harrison County)</t>
+          <t>Y--MI-SENEY NWR-DC DAM DECOMMISIONING</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
         <is>
-          <t>Biloxi, Mississippi</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E79" s="20" t="inlineStr">
@@ -13489,12 +13813,12 @@
       </c>
       <c r="H79" s="20" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="J79" s="20" t="inlineStr">
@@ -13511,12 +13835,12 @@
     <row r="80" ht="28" customHeight="1">
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>W912P926BA007</t>
+          <t>W9127N26BA015</t>
         </is>
       </c>
       <c r="C80" s="30" t="inlineStr">
         <is>
-          <t>Crains Island Stage 3</t>
+          <t>Oregon/Washington Clamshell Maintenance Dredging 2026</t>
         </is>
       </c>
       <c r="D80" s="17" t="inlineStr">
@@ -13541,12 +13865,12 @@
       </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="I80" s="17" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="J80" s="17" t="inlineStr">
@@ -13563,12 +13887,12 @@
     <row r="81" ht="28" customHeight="1">
       <c r="B81" s="20" t="inlineStr">
         <is>
-          <t>140P5326R0006</t>
+          <t>140P8326Q0041</t>
         </is>
       </c>
       <c r="C81" s="33" t="inlineStr">
         <is>
-          <t>MACA-REHAB ENTRANCE SIGNS/PARKING AREAS</t>
+          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
@@ -13578,7 +13902,7 @@
       </c>
       <c r="E81" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
@@ -13593,12 +13917,12 @@
       </c>
       <c r="H81" s="20" t="inlineStr">
         <is>
-          <t>Jul 08, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>28d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="J81" s="20" t="inlineStr">
@@ -13615,17 +13939,17 @@
     <row r="82" ht="28" customHeight="1">
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>140P6426B0008</t>
+          <t>W9127826RA046</t>
         </is>
       </c>
       <c r="C82" s="30" t="inlineStr">
         <is>
-          <t>Z--ZION- Crawford Dam Removal and Diversion</t>
+          <t>Deer Island Ecosystem Restoration, Phase 1 Deer Island, MS (Harrison County)</t>
         </is>
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Biloxi, Mississippi</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
@@ -13645,12 +13969,12 @@
       </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>Jul 08, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="I82" s="17" t="inlineStr">
         <is>
-          <t>28d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="J82" s="17" t="inlineStr">
@@ -13667,12 +13991,12 @@
     <row r="83" ht="28" customHeight="1">
       <c r="B83" s="20" t="inlineStr">
         <is>
-          <t>N6247326R9953</t>
+          <t>W912P926BA007</t>
         </is>
       </c>
       <c r="C83" s="33" t="inlineStr">
         <is>
-          <t>Base Operations Support Contract (BOSC) for Naval Air Weapons Station (NAWS) China Lake, California and Other Locations as Approved</t>
+          <t>Crains Island Stage 3</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -13682,7 +14006,7 @@
       </c>
       <c r="E83" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F83" s="20" t="inlineStr">
@@ -13692,17 +14016,17 @@
       </c>
       <c r="G83" s="20" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H83" s="20" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>30d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="J83" s="20" t="inlineStr">
@@ -13719,12 +14043,12 @@
     <row r="84" ht="28" customHeight="1">
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>140R4026R0010</t>
+          <t>FA282326R0014</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>J--GC26 FIRE ALARM SYSTEM REPLACEMENT</t>
+          <t xml:space="preserve">RELOCATABLE FACILITY (RFL) MAINTENANCE AND REPAIR SERVICES - EGLIN AFB </t>
         </is>
       </c>
       <c r="D84" s="17" t="inlineStr">
@@ -13734,7 +14058,7 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F84" s="17" t="inlineStr">
@@ -13749,12 +14073,12 @@
       </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
-          <t>30d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="J84" s="17" t="inlineStr">
@@ -13771,12 +14095,12 @@
     <row r="85" ht="28" customHeight="1">
       <c r="B85" s="20" t="inlineStr">
         <is>
-          <t>N6247326R0053</t>
+          <t>140P5326R0006</t>
         </is>
       </c>
       <c r="C85" s="33" t="inlineStr">
         <is>
-          <t>CHINA LAKE BOSC - SOLICITATION - N6247326R0053</t>
+          <t>MACA-REHAB ENTRANCE SIGNS/PARKING AREAS</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
@@ -13786,7 +14110,7 @@
       </c>
       <c r="E85" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F85" s="20" t="inlineStr">
@@ -13801,12 +14125,12 @@
       </c>
       <c r="H85" s="20" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 08, 2026</t>
         </is>
       </c>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>30d</t>
+          <t>28d</t>
         </is>
       </c>
       <c r="J85" s="20" t="inlineStr">
@@ -13823,12 +14147,12 @@
     <row r="86" ht="28" customHeight="1">
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>W9128F26RA056</t>
+          <t>140P6426B0008</t>
         </is>
       </c>
       <c r="C86" s="30" t="inlineStr">
         <is>
-          <t>Solicitation for Grand Forks Fueling System Repairs</t>
+          <t>Z--ZION- Crawford Dam Removal and Diversion</t>
         </is>
       </c>
       <c r="D86" s="17" t="inlineStr">
@@ -13838,7 +14162,7 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>237120</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F86" s="17" t="inlineStr">
@@ -13853,12 +14177,12 @@
       </c>
       <c r="H86" s="17" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 08, 2026</t>
         </is>
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
-          <t>30d</t>
+          <t>28d</t>
         </is>
       </c>
       <c r="J86" s="17" t="inlineStr">
@@ -13875,12 +14199,12 @@
     <row r="87" ht="28" customHeight="1">
       <c r="B87" s="20" t="inlineStr">
         <is>
-          <t>140L3626Q0032</t>
+          <t>N6247326R9953</t>
         </is>
       </c>
       <c r="C87" s="33" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>Base Operations Support Contract (BOSC) for Naval Air Weapons Station (NAWS) China Lake, California and Other Locations as Approved</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
@@ -13890,7 +14214,7 @@
       </c>
       <c r="E87" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F87" s="20" t="inlineStr">
@@ -13900,17 +14224,17 @@
       </c>
       <c r="G87" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$47.0M</t>
         </is>
       </c>
       <c r="H87" s="20" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 10, 2026</t>
         </is>
       </c>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>35d</t>
+          <t>30d</t>
         </is>
       </c>
       <c r="J87" s="20" t="inlineStr">
@@ -13925,52 +14249,52 @@
       </c>
     </row>
     <row r="88" ht="28" customHeight="1">
-      <c r="B88" s="37" t="inlineStr">
-        <is>
-          <t>36C25626R0015</t>
-        </is>
-      </c>
-      <c r="C88" s="25" t="inlineStr">
-        <is>
-          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
-        </is>
-      </c>
-      <c r="D88" s="37" t="inlineStr">
-        <is>
-          <t>Fayetteville, Arkansas</t>
-        </is>
-      </c>
-      <c r="E88" s="37" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="F88" s="37" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G88" s="37" t="inlineStr">
-        <is>
-          <t>$15.0M</t>
-        </is>
-      </c>
-      <c r="H88" s="37" t="inlineStr">
-        <is>
-          <t>Jul 23, 2026</t>
-        </is>
-      </c>
-      <c r="I88" s="37" t="inlineStr">
-        <is>
-          <t>43d</t>
-        </is>
-      </c>
-      <c r="J88" s="37" t="inlineStr">
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>140R4026R0010</t>
+        </is>
+      </c>
+      <c r="C88" s="30" t="inlineStr">
+        <is>
+          <t>J--GC26 FIRE ALARM SYSTEM REPLACEMENT</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>Jul 10, 2026</t>
+        </is>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>30d</t>
+        </is>
+      </c>
+      <c r="J88" s="17" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K88" s="40" t="inlineStr">
+      <c r="K88" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -13979,22 +14303,22 @@
     <row r="89" ht="28" customHeight="1">
       <c r="B89" s="20" t="inlineStr">
         <is>
-          <t>140P6026Q0042</t>
+          <t>N6247326R0053</t>
         </is>
       </c>
       <c r="C89" s="33" t="inlineStr">
         <is>
-          <t>Z--FOLS, Replace Alarm System &amp; Electrical Panel</t>
+          <t>CHINA LAKE BOSC - SOLICITATION - N6247326R0053</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
         <is>
-          <t>Larned, Kansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E89" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F89" s="20" t="inlineStr">
@@ -14009,12 +14333,12 @@
       </c>
       <c r="H89" s="20" t="inlineStr">
         <is>
-          <t>Jun 10, 2026</t>
+          <t>Jul 10, 2026</t>
         </is>
       </c>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>30d</t>
         </is>
       </c>
       <c r="J89" s="20" t="inlineStr">
@@ -14031,22 +14355,22 @@
     <row r="90" ht="28" customHeight="1">
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>W9123826BA011</t>
+          <t>W9128F26RA056</t>
         </is>
       </c>
       <c r="C90" s="30" t="inlineStr">
         <is>
-          <t>Rail Curves Package 3 for MOTCO, CA</t>
+          <t>Solicitation for Grand Forks Fueling System Repairs</t>
         </is>
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t>Concord, California</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237120</t>
         </is>
       </c>
       <c r="F90" s="17" t="inlineStr">
@@ -14056,22 +14380,22 @@
       </c>
       <c r="G90" s="17" t="inlineStr">
         <is>
-          <t>$7.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H90" s="17" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jul 10, 2026</t>
         </is>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>30d</t>
         </is>
       </c>
       <c r="J90" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="K90" s="32" t="inlineStr">
@@ -14083,22 +14407,22 @@
     <row r="91" ht="28" customHeight="1">
       <c r="B91" s="20" t="inlineStr">
         <is>
-          <t>EQPMBE-26-0203</t>
+          <t>140L3626Q0032</t>
         </is>
       </c>
       <c r="C91" s="33" t="inlineStr">
         <is>
-          <t>USAO Schwartz Conference Room Display Upgrade</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E91" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F91" s="20" t="inlineStr">
@@ -14113,17 +14437,17 @@
       </c>
       <c r="H91" s="20" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I91" s="20" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>35d</t>
         </is>
       </c>
       <c r="J91" s="20" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="K91" s="35" t="inlineStr">
@@ -14135,22 +14459,22 @@
     <row r="92" ht="28" customHeight="1">
       <c r="B92" s="37" t="inlineStr">
         <is>
-          <t>36C24826R0107</t>
+          <t>36C25626R0015</t>
         </is>
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>J061--PROJECT 675-25-804, Bid-Build (BB) Install Water Tower  Projector System at Lake Nona</t>
+          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
         </is>
       </c>
       <c r="D92" s="37" t="inlineStr">
         <is>
-          <t>Orlando, Florida</t>
+          <t>Fayetteville, Arkansas</t>
         </is>
       </c>
       <c r="E92" s="37" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F92" s="37" t="inlineStr">
@@ -14160,22 +14484,22 @@
       </c>
       <c r="G92" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$15.0M</t>
         </is>
       </c>
       <c r="H92" s="37" t="inlineStr">
         <is>
-          <t>Jun 15, 2026</t>
+          <t>Jul 23, 2026</t>
         </is>
       </c>
       <c r="I92" s="37" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>43d</t>
         </is>
       </c>
       <c r="J92" s="37" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="K92" s="40" t="inlineStr">
@@ -14187,22 +14511,22 @@
     <row r="93" ht="28" customHeight="1">
       <c r="B93" s="20" t="inlineStr">
         <is>
-          <t>W912HN26BA008</t>
+          <t>140P6026Q0042</t>
         </is>
       </c>
       <c r="C93" s="33" t="inlineStr">
         <is>
-          <t>FY26 Brunswick Inner Harbor Dredging Project</t>
+          <t>Z--FOLS, Replace Alarm System &amp; Electrical Panel</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Larned, Kansas</t>
         </is>
       </c>
       <c r="E93" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F93" s="20" t="inlineStr">
@@ -14217,17 +14541,17 @@
       </c>
       <c r="H93" s="20" t="inlineStr">
         <is>
-          <t>Jun 15, 2026</t>
+          <t>Jun 10, 2026</t>
         </is>
       </c>
       <c r="I93" s="20" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J93" s="20" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="K93" s="35" t="inlineStr">
@@ -14239,17 +14563,17 @@
     <row r="94" ht="28" customHeight="1">
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>W912BU26BA026</t>
+          <t>W9123826BA011</t>
         </is>
       </c>
       <c r="C94" s="30" t="inlineStr">
         <is>
-          <t>Absecon Island Outfalls Repair</t>
+          <t>Rail Curves Package 3 for MOTCO, CA</t>
         </is>
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Concord, California</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
@@ -14264,17 +14588,17 @@
       </c>
       <c r="G94" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$7.5M</t>
         </is>
       </c>
       <c r="H94" s="17" t="inlineStr">
         <is>
-          <t>Jun 16, 2026</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="J94" s="17" t="inlineStr">
@@ -14291,22 +14615,22 @@
     <row r="95" ht="28" customHeight="1">
       <c r="B95" s="20" t="inlineStr">
         <is>
-          <t>FA301626FB0001</t>
+          <t>EQPMBE-26-0203</t>
         </is>
       </c>
       <c r="C95" s="33" t="inlineStr">
         <is>
-          <t>Repair Carswell Ave.</t>
+          <t>USAO Schwartz Conference Room Display Upgrade</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
         <is>
-          <t>DWG, Texas</t>
+          <t>California</t>
         </is>
       </c>
       <c r="E95" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
@@ -14321,12 +14645,12 @@
       </c>
       <c r="H95" s="20" t="inlineStr">
         <is>
-          <t>Jun 17, 2026</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="I95" s="20" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="J95" s="20" t="inlineStr">
@@ -14343,102 +14667,102 @@
     <row r="96" ht="28" customHeight="1">
       <c r="B96" s="37" t="inlineStr">
         <is>
-          <t>36C25026B0050</t>
+          <t>36C24826R0107</t>
         </is>
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>Z1DA--Project No. 552-26-202 - Replace Overhead Paging System</t>
+          <t>J061--PROJECT 675-25-804, Bid-Build (BB) Install Water Tower  Projector System at Lake Nona</t>
         </is>
       </c>
       <c r="D96" s="37" t="inlineStr">
         <is>
+          <t>Orlando, Florida</t>
+        </is>
+      </c>
+      <c r="E96" s="37" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F96" s="37" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G96" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H96" s="37" t="inlineStr">
+        <is>
+          <t>Jun 15, 2026</t>
+        </is>
+      </c>
+      <c r="I96" s="37" t="inlineStr">
+        <is>
+          <t>5d</t>
+        </is>
+      </c>
+      <c r="J96" s="37" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K96" s="40" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="28" customHeight="1">
+      <c r="B97" s="20" t="inlineStr">
+        <is>
+          <t>W912HN26BA008</t>
+        </is>
+      </c>
+      <c r="C97" s="33" t="inlineStr">
+        <is>
+          <t>FY26 Brunswick Inner Harbor Dredging Project</t>
+        </is>
+      </c>
+      <c r="D97" s="20" t="inlineStr">
+        <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E96" s="37" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F96" s="37" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G96" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H96" s="37" t="inlineStr">
-        <is>
-          <t>Jun 17, 2026</t>
-        </is>
-      </c>
-      <c r="I96" s="37" t="inlineStr">
-        <is>
-          <t>7d</t>
-        </is>
-      </c>
-      <c r="J96" s="37" t="inlineStr">
+      <c r="E97" s="20" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F97" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G97" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H97" s="20" t="inlineStr">
+        <is>
+          <t>Jun 15, 2026</t>
+        </is>
+      </c>
+      <c r="I97" s="20" t="inlineStr">
+        <is>
+          <t>5d</t>
+        </is>
+      </c>
+      <c r="J97" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K96" s="40" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="28" customHeight="1">
-      <c r="B97" s="37" t="inlineStr">
-        <is>
-          <t>36C25026B0045</t>
-        </is>
-      </c>
-      <c r="C97" s="25" t="inlineStr">
-        <is>
-          <t>Z2LC--Campus Sinkhole Repair  552-26-506</t>
-        </is>
-      </c>
-      <c r="D97" s="37" t="inlineStr">
-        <is>
-          <t>Dayton, Ohio</t>
-        </is>
-      </c>
-      <c r="E97" s="37" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="F97" s="37" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G97" s="37" t="inlineStr">
-        <is>
-          <t>$750K</t>
-        </is>
-      </c>
-      <c r="H97" s="37" t="inlineStr">
-        <is>
-          <t>Jun 18, 2026</t>
-        </is>
-      </c>
-      <c r="I97" s="37" t="inlineStr">
-        <is>
-          <t>8d</t>
-        </is>
-      </c>
-      <c r="J97" s="37" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K97" s="40" t="inlineStr">
+      <c r="K97" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14447,12 +14771,12 @@
     <row r="98" ht="28" customHeight="1">
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>W911WN26RA011</t>
+          <t>W912BU26BA026</t>
         </is>
       </c>
       <c r="C98" s="30" t="inlineStr">
         <is>
-          <t>Install 4 Corners Hydraulics at Dashields Locks and Dam</t>
+          <t>Absecon Island Outfalls Repair</t>
         </is>
       </c>
       <c r="D98" s="17" t="inlineStr">
@@ -14477,12 +14801,12 @@
       </c>
       <c r="H98" s="17" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>Jun 16, 2026</t>
         </is>
       </c>
       <c r="I98" s="17" t="inlineStr">
         <is>
-          <t>8d</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="J98" s="17" t="inlineStr">
@@ -14499,154 +14823,154 @@
     <row r="99" ht="28" customHeight="1">
       <c r="B99" s="20" t="inlineStr">
         <is>
-          <t>140P6026Q0052</t>
+          <t>FA301626FB0001</t>
         </is>
       </c>
       <c r="C99" s="33" t="inlineStr">
         <is>
-          <t>Z--WACO Emergency Generator</t>
+          <t>Repair Carswell Ave.</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
         <is>
-          <t>Waco, Texas</t>
+          <t>DWG, Texas</t>
         </is>
       </c>
       <c r="E99" s="20" t="inlineStr">
         <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F99" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G99" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H99" s="20" t="inlineStr">
+        <is>
+          <t>Jun 17, 2026</t>
+        </is>
+      </c>
+      <c r="I99" s="20" t="inlineStr">
+        <is>
+          <t>7d</t>
+        </is>
+      </c>
+      <c r="J99" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K99" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="28" customHeight="1">
+      <c r="B100" s="37" t="inlineStr">
+        <is>
+          <t>36C25026B0050</t>
+        </is>
+      </c>
+      <c r="C100" s="25" t="inlineStr">
+        <is>
+          <t>Z1DA--Project No. 552-26-202 - Replace Overhead Paging System</t>
+        </is>
+      </c>
+      <c r="D100" s="37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E100" s="37" t="inlineStr">
+        <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F99" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G99" s="20" t="inlineStr">
-        <is>
-          <t>$62K</t>
-        </is>
-      </c>
-      <c r="H99" s="20" t="inlineStr">
+      <c r="F100" s="37" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G100" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H100" s="37" t="inlineStr">
+        <is>
+          <t>Jun 17, 2026</t>
+        </is>
+      </c>
+      <c r="I100" s="37" t="inlineStr">
+        <is>
+          <t>7d</t>
+        </is>
+      </c>
+      <c r="J100" s="37" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K100" s="40" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="B101" s="37" t="inlineStr">
+        <is>
+          <t>36C25026B0045</t>
+        </is>
+      </c>
+      <c r="C101" s="25" t="inlineStr">
+        <is>
+          <t>Z2LC--Campus Sinkhole Repair  552-26-506</t>
+        </is>
+      </c>
+      <c r="D101" s="37" t="inlineStr">
+        <is>
+          <t>Dayton, Ohio</t>
+        </is>
+      </c>
+      <c r="E101" s="37" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F101" s="37" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G101" s="37" t="inlineStr">
+        <is>
+          <t>$750K</t>
+        </is>
+      </c>
+      <c r="H101" s="37" t="inlineStr">
         <is>
           <t>Jun 18, 2026</t>
         </is>
       </c>
-      <c r="I99" s="20" t="inlineStr">
+      <c r="I101" s="37" t="inlineStr">
         <is>
           <t>8d</t>
         </is>
       </c>
-      <c r="J99" s="20" t="inlineStr">
+      <c r="J101" s="37" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K99" s="35" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="28" customHeight="1">
-      <c r="B100" s="17" t="inlineStr">
-        <is>
-          <t>36C25226Q0426</t>
-        </is>
-      </c>
-      <c r="C100" s="30" t="inlineStr">
-        <is>
-          <t>J065--Variable Frequency Drive Maintenance</t>
-        </is>
-      </c>
-      <c r="D100" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E100" s="17" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F100" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G100" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H100" s="17" t="inlineStr">
-        <is>
-          <t>Jun 22, 2026</t>
-        </is>
-      </c>
-      <c r="I100" s="17" t="inlineStr">
-        <is>
-          <t>12d</t>
-        </is>
-      </c>
-      <c r="J100" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K100" s="32" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="28" customHeight="1">
-      <c r="B101" s="20" t="inlineStr">
-        <is>
-          <t>36C24526Q0576</t>
-        </is>
-      </c>
-      <c r="C101" s="33" t="inlineStr">
-        <is>
-          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
-        </is>
-      </c>
-      <c r="D101" s="20" t="inlineStr">
-        <is>
-          <t>Baltimore, MD</t>
-        </is>
-      </c>
-      <c r="E101" s="20" t="inlineStr">
-        <is>
-          <t>561210</t>
-        </is>
-      </c>
-      <c r="F101" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G101" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H101" s="20" t="inlineStr">
-        <is>
-          <t>Jun 22, 2026</t>
-        </is>
-      </c>
-      <c r="I101" s="20" t="inlineStr">
-        <is>
-          <t>12d</t>
-        </is>
-      </c>
-      <c r="J101" s="20" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K101" s="35" t="inlineStr">
+      <c r="K101" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14655,22 +14979,22 @@
     <row r="102" ht="28" customHeight="1">
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>FDA-PRESOL-132892</t>
+          <t>W911WN26RA011</t>
         </is>
       </c>
       <c r="C102" s="30" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>Install 4 Corners Hydraulics at Dashields Locks and Dam</t>
         </is>
       </c>
       <c r="D102" s="17" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F102" s="17" t="inlineStr">
@@ -14680,17 +15004,17 @@
       </c>
       <c r="G102" s="17" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H102" s="17" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="I102" s="17" t="inlineStr">
         <is>
-          <t>12d</t>
+          <t>8d</t>
         </is>
       </c>
       <c r="J102" s="17" t="inlineStr">
@@ -14707,22 +15031,22 @@
     <row r="103" ht="28" customHeight="1">
       <c r="B103" s="20" t="inlineStr">
         <is>
-          <t>W912PM26RA0003</t>
+          <t>140P6026Q0052</t>
         </is>
       </c>
       <c r="C103" s="33" t="inlineStr">
         <is>
-          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
+          <t>Z--WACO Emergency Generator</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Waco, Texas</t>
         </is>
       </c>
       <c r="E103" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
@@ -14732,17 +15056,17 @@
       </c>
       <c r="G103" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$62K</t>
         </is>
       </c>
       <c r="H103" s="20" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="I103" s="20" t="inlineStr">
         <is>
-          <t>13d</t>
+          <t>8d</t>
         </is>
       </c>
       <c r="J103" s="20" t="inlineStr">
@@ -14759,12 +15083,12 @@
     <row r="104" ht="28" customHeight="1">
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>W50S7X-26-B-A003</t>
+          <t>36C25226Q0426</t>
         </is>
       </c>
       <c r="C104" s="30" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>J065--Variable Frequency Drive Maintenance</t>
         </is>
       </c>
       <c r="D104" s="17" t="inlineStr">
@@ -14784,17 +15108,17 @@
       </c>
       <c r="G104" s="17" t="inlineStr">
         <is>
-          <t>$5.1M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H104" s="17" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="I104" s="17" t="inlineStr">
         <is>
-          <t>13d</t>
+          <t>12d</t>
         </is>
       </c>
       <c r="J104" s="17" t="inlineStr">
@@ -14811,22 +15135,22 @@
     <row r="105" ht="28" customHeight="1">
       <c r="B105" s="20" t="inlineStr">
         <is>
-          <t>GROUP1-24-R-W001</t>
+          <t>36C24526Q0576</t>
         </is>
       </c>
       <c r="C105" s="33" t="inlineStr">
         <is>
-          <t>Atlantic Intracoastal Waterway Maintenance Dredging</t>
+          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="E105" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
@@ -14836,17 +15160,17 @@
       </c>
       <c r="G105" s="20" t="inlineStr">
         <is>
-          <t>$17.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H105" s="20" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="I105" s="20" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>12d</t>
         </is>
       </c>
       <c r="J105" s="20" t="inlineStr">
@@ -14861,52 +15185,52 @@
       </c>
     </row>
     <row r="106" ht="28" customHeight="1">
-      <c r="B106" s="37" t="inlineStr">
-        <is>
-          <t>36C26126R0050</t>
-        </is>
-      </c>
-      <c r="C106" s="25" t="inlineStr">
-        <is>
-          <t>6150--FY26 NRM 654-26-020 | 654-26-2-6059-0042 | Bldg 12 Pump  Power Relocation | VA Sierra Nevada Health Care System  Reno, NV</t>
-        </is>
-      </c>
-      <c r="D106" s="37" t="inlineStr">
-        <is>
-          <t>Reno, NV</t>
-        </is>
-      </c>
-      <c r="E106" s="37" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F106" s="37" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G106" s="37" t="inlineStr">
-        <is>
-          <t>$5.0M</t>
-        </is>
-      </c>
-      <c r="H106" s="37" t="inlineStr">
-        <is>
-          <t>Jun 24, 2026</t>
-        </is>
-      </c>
-      <c r="I106" s="37" t="inlineStr">
-        <is>
-          <t>14d</t>
-        </is>
-      </c>
-      <c r="J106" s="37" t="inlineStr">
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>FDA-PRESOL-132892</t>
+        </is>
+      </c>
+      <c r="C106" s="30" t="inlineStr">
+        <is>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+        </is>
+      </c>
+      <c r="D106" s="17" t="inlineStr">
+        <is>
+          <t>Jefferson, Arkansas</t>
+        </is>
+      </c>
+      <c r="E106" s="17" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="F106" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G106" s="17" t="inlineStr">
+        <is>
+          <t>$47.0M</t>
+        </is>
+      </c>
+      <c r="H106" s="17" t="inlineStr">
+        <is>
+          <t>Jun 22, 2026</t>
+        </is>
+      </c>
+      <c r="I106" s="17" t="inlineStr">
+        <is>
+          <t>12d</t>
+        </is>
+      </c>
+      <c r="J106" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K106" s="40" t="inlineStr">
+      <c r="K106" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14915,12 +15239,12 @@
     <row r="107" ht="28" customHeight="1">
       <c r="B107" s="20" t="inlineStr">
         <is>
-          <t>693C73-26-R-000047</t>
+          <t>W912PM26RA0003</t>
         </is>
       </c>
       <c r="C107" s="33" t="inlineStr">
         <is>
-          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
+          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
@@ -14930,7 +15254,7 @@
       </c>
       <c r="E107" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
@@ -14940,17 +15264,17 @@
       </c>
       <c r="G107" s="20" t="inlineStr">
         <is>
-          <t>$12.9M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H107" s="20" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="I107" s="20" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>13d</t>
         </is>
       </c>
       <c r="J107" s="20" t="inlineStr">
@@ -14967,22 +15291,22 @@
     <row r="108" ht="28" customHeight="1">
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>W9128F26BA019</t>
+          <t>W50S7X-26-B-A003</t>
         </is>
       </c>
       <c r="C108" s="30" t="inlineStr">
         <is>
-          <t>Oahe IDCC Road Maintenance 2026</t>
+          <t>B16 PLC Replacement</t>
         </is>
       </c>
       <c r="D108" s="17" t="inlineStr">
         <is>
-          <t>Fort Pierre, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F108" s="17" t="inlineStr">
@@ -14992,17 +15316,17 @@
       </c>
       <c r="G108" s="17" t="inlineStr">
         <is>
-          <t>$21.5M</t>
+          <t>$5.1M</t>
         </is>
       </c>
       <c r="H108" s="17" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="I108" s="17" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>13d</t>
         </is>
       </c>
       <c r="J108" s="17" t="inlineStr">
@@ -15017,104 +15341,104 @@
       </c>
     </row>
     <row r="109" ht="28" customHeight="1">
-      <c r="B109" s="37" t="inlineStr">
-        <is>
-          <t>36C24626R0067</t>
-        </is>
-      </c>
-      <c r="C109" s="25" t="inlineStr">
-        <is>
-          <t>Z2DA--FY26 NRM  590-24-115 Public Address System</t>
-        </is>
-      </c>
-      <c r="D109" s="37" t="inlineStr">
-        <is>
-          <t>Hampton, Virginia</t>
-        </is>
-      </c>
-      <c r="E109" s="37" t="inlineStr">
+      <c r="B109" s="20" t="inlineStr">
+        <is>
+          <t>GROUP1-24-R-W001</t>
+        </is>
+      </c>
+      <c r="C109" s="33" t="inlineStr">
+        <is>
+          <t>Atlantic Intracoastal Waterway Maintenance Dredging</t>
+        </is>
+      </c>
+      <c r="D109" s="20" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="E109" s="20" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F109" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G109" s="20" t="inlineStr">
+        <is>
+          <t>$17.5M</t>
+        </is>
+      </c>
+      <c r="H109" s="20" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="I109" s="20" t="inlineStr">
+        <is>
+          <t>14d</t>
+        </is>
+      </c>
+      <c r="J109" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K109" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="28" customHeight="1">
+      <c r="B110" s="37" t="inlineStr">
+        <is>
+          <t>36C26126R0050</t>
+        </is>
+      </c>
+      <c r="C110" s="25" t="inlineStr">
+        <is>
+          <t>6150--FY26 NRM 654-26-020 | 654-26-2-6059-0042 | Bldg 12 Pump  Power Relocation | VA Sierra Nevada Health Care System  Reno, NV</t>
+        </is>
+      </c>
+      <c r="D110" s="37" t="inlineStr">
+        <is>
+          <t>Reno, NV</t>
+        </is>
+      </c>
+      <c r="E110" s="37" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F109" s="37" t="inlineStr">
+      <c r="F110" s="37" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G109" s="37" t="inlineStr">
-        <is>
-          <t>$7.0M</t>
-        </is>
-      </c>
-      <c r="H109" s="37" t="inlineStr">
-        <is>
-          <t>Jul 13, 2026</t>
-        </is>
-      </c>
-      <c r="I109" s="37" t="inlineStr">
-        <is>
-          <t>33d</t>
-        </is>
-      </c>
-      <c r="J109" s="37" t="inlineStr">
+      <c r="G110" s="37" t="inlineStr">
+        <is>
+          <t>$5.0M</t>
+        </is>
+      </c>
+      <c r="H110" s="37" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="I110" s="37" t="inlineStr">
+        <is>
+          <t>14d</t>
+        </is>
+      </c>
+      <c r="J110" s="37" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K109" s="40" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="28" customHeight="1">
-      <c r="B110" s="17" t="inlineStr">
-        <is>
-          <t>140L2626R0004</t>
-        </is>
-      </c>
-      <c r="C110" s="30" t="inlineStr">
-        <is>
-          <t>Y--Cauldron Linn Recreation Site Improvements</t>
-        </is>
-      </c>
-      <c r="D110" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E110" s="17" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F110" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G110" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H110" s="17" t="inlineStr">
-        <is>
-          <t>Jul 13, 2026</t>
-        </is>
-      </c>
-      <c r="I110" s="17" t="inlineStr">
-        <is>
-          <t>33d</t>
-        </is>
-      </c>
-      <c r="J110" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K110" s="32" t="inlineStr">
+      <c r="K110" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15123,12 +15447,12 @@
     <row r="111" ht="28" customHeight="1">
       <c r="B111" s="20" t="inlineStr">
         <is>
-          <t>140L2626Q0032</t>
+          <t>693C73-26-R-000047</t>
         </is>
       </c>
       <c r="C111" s="33" t="inlineStr">
         <is>
-          <t>Y--Indian Springs Vault Toilet</t>
+          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
@@ -15138,7 +15462,7 @@
       </c>
       <c r="E111" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F111" s="20" t="inlineStr">
@@ -15148,17 +15472,17 @@
       </c>
       <c r="G111" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$12.9M</t>
         </is>
       </c>
       <c r="H111" s="20" t="inlineStr">
         <is>
-          <t>Jul 13, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="I111" s="20" t="inlineStr">
         <is>
-          <t>33d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="J111" s="20" t="inlineStr">
@@ -15175,22 +15499,22 @@
     <row r="112" ht="28" customHeight="1">
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>89503426BWA000068</t>
+          <t>W9128F26BA019</t>
         </is>
       </c>
       <c r="C112" s="30" t="inlineStr">
         <is>
-          <t>Y--Beresford Substation Stage 11, South Dakota</t>
+          <t>Oahe IDCC Road Maintenance 2026</t>
         </is>
       </c>
       <c r="D112" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Fort Pierre, South Dakota</t>
         </is>
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F112" s="17" t="inlineStr">
@@ -15200,17 +15524,17 @@
       </c>
       <c r="G112" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$21.5M</t>
         </is>
       </c>
       <c r="H112" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="I112" s="17" t="inlineStr">
         <is>
-          <t>35d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="J112" s="17" t="inlineStr">
@@ -15225,52 +15549,52 @@
       </c>
     </row>
     <row r="113" ht="28" customHeight="1">
-      <c r="B113" s="20" t="inlineStr">
-        <is>
-          <t>W912EE26RA015</t>
-        </is>
-      </c>
-      <c r="C113" s="33" t="inlineStr">
-        <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
-        </is>
-      </c>
-      <c r="D113" s="20" t="inlineStr">
-        <is>
-          <t>Royal, Arkansas</t>
-        </is>
-      </c>
-      <c r="E113" s="20" t="inlineStr">
-        <is>
-          <t>561210</t>
-        </is>
-      </c>
-      <c r="F113" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G113" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H113" s="20" t="inlineStr">
-        <is>
-          <t>Jul 15, 2026</t>
-        </is>
-      </c>
-      <c r="I113" s="20" t="inlineStr">
-        <is>
-          <t>35d</t>
-        </is>
-      </c>
-      <c r="J113" s="20" t="inlineStr">
+      <c r="B113" s="37" t="inlineStr">
+        <is>
+          <t>36C24626R0067</t>
+        </is>
+      </c>
+      <c r="C113" s="25" t="inlineStr">
+        <is>
+          <t>Z2DA--FY26 NRM  590-24-115 Public Address System</t>
+        </is>
+      </c>
+      <c r="D113" s="37" t="inlineStr">
+        <is>
+          <t>Hampton, Virginia</t>
+        </is>
+      </c>
+      <c r="E113" s="37" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F113" s="37" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G113" s="37" t="inlineStr">
+        <is>
+          <t>$7.0M</t>
+        </is>
+      </c>
+      <c r="H113" s="37" t="inlineStr">
+        <is>
+          <t>Jul 13, 2026</t>
+        </is>
+      </c>
+      <c r="I113" s="37" t="inlineStr">
+        <is>
+          <t>33d</t>
+        </is>
+      </c>
+      <c r="J113" s="37" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K113" s="35" t="inlineStr">
+      <c r="K113" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15279,12 +15603,12 @@
     <row r="114" ht="28" customHeight="1">
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>140L2626R0003</t>
+          <t>140L2626R0004</t>
         </is>
       </c>
       <c r="C114" s="30" t="inlineStr">
         <is>
-          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
+          <t>Y--Cauldron Linn Recreation Site Improvements</t>
         </is>
       </c>
       <c r="D114" s="17" t="inlineStr">
@@ -15294,7 +15618,7 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F114" s="17" t="inlineStr">
@@ -15309,12 +15633,12 @@
       </c>
       <c r="H114" s="17" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="I114" s="17" t="inlineStr">
         <is>
-          <t>42d</t>
+          <t>33d</t>
         </is>
       </c>
       <c r="J114" s="17" t="inlineStr">
@@ -15331,12 +15655,12 @@
     <row r="115" ht="28" customHeight="1">
       <c r="B115" s="20" t="inlineStr">
         <is>
-          <t>140L2626Q0033</t>
+          <t>140L2626Q0032</t>
         </is>
       </c>
       <c r="C115" s="33" t="inlineStr">
         <is>
-          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
+          <t>Y--Indian Springs Vault Toilet</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
@@ -15361,12 +15685,12 @@
       </c>
       <c r="H115" s="20" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="I115" s="20" t="inlineStr">
         <is>
-          <t>42d</t>
+          <t>33d</t>
         </is>
       </c>
       <c r="J115" s="20" t="inlineStr">
@@ -15383,12 +15707,12 @@
     <row r="116" ht="28" customHeight="1">
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0016</t>
+          <t>89503426BWA000068</t>
         </is>
       </c>
       <c r="C116" s="30" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>Y--Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="D116" s="17" t="inlineStr">
@@ -15398,7 +15722,7 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F116" s="17" t="inlineStr">
@@ -15413,12 +15737,12 @@
       </c>
       <c r="H116" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I116" s="17" t="inlineStr">
         <is>
-          <t>44d</t>
+          <t>35d</t>
         </is>
       </c>
       <c r="J116" s="17" t="inlineStr">
@@ -15435,22 +15759,22 @@
     <row r="117" ht="28" customHeight="1">
       <c r="B117" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0015</t>
+          <t>W912EE26RA015</t>
         </is>
       </c>
       <c r="C117" s="33" t="inlineStr">
         <is>
-          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E117" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
@@ -15465,12 +15789,12 @@
       </c>
       <c r="H117" s="20" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I117" s="20" t="inlineStr">
         <is>
-          <t>44d</t>
+          <t>35d</t>
         </is>
       </c>
       <c r="J117" s="20" t="inlineStr">
@@ -15487,12 +15811,12 @@
     <row r="118" ht="28" customHeight="1">
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0024</t>
+          <t>140L2626R0003</t>
         </is>
       </c>
       <c r="C118" s="30" t="inlineStr">
         <is>
-          <t>Y--Sherburne NWR South Loop Autotour Rehab</t>
+          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
         </is>
       </c>
       <c r="D118" s="17" t="inlineStr">
@@ -15512,17 +15836,17 @@
       </c>
       <c r="G118" s="17" t="inlineStr">
         <is>
-          <t>$11.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H118" s="17" t="inlineStr">
         <is>
-          <t>Jul 27, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I118" s="17" t="inlineStr">
         <is>
-          <t>47d</t>
+          <t>42d</t>
         </is>
       </c>
       <c r="J118" s="17" t="inlineStr">
@@ -15539,12 +15863,12 @@
     <row r="119" ht="28" customHeight="1">
       <c r="B119" s="20" t="inlineStr">
         <is>
-          <t>140L3726R0006</t>
+          <t>140L2626Q0033</t>
         </is>
       </c>
       <c r="C119" s="33" t="inlineStr">
         <is>
-          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
@@ -15554,7 +15878,7 @@
       </c>
       <c r="E119" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
@@ -15564,17 +15888,17 @@
       </c>
       <c r="G119" s="20" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H119" s="20" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I119" s="20" t="inlineStr">
         <is>
-          <t>79d</t>
+          <t>42d</t>
         </is>
       </c>
       <c r="J119" s="20" t="inlineStr">
@@ -15591,12 +15915,12 @@
     <row r="120" ht="28" customHeight="1">
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>36C25226Q0359</t>
+          <t>140P5426R0016</t>
         </is>
       </c>
       <c r="C120" s="30" t="inlineStr">
         <is>
-          <t>J059--Triennial Electical Panel Maintenance and Survey</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D120" s="17" t="inlineStr">
@@ -15606,7 +15930,7 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F120" s="17" t="inlineStr">
@@ -15621,12 +15945,12 @@
       </c>
       <c r="H120" s="17" t="inlineStr">
         <is>
-          <t>Jun 10, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I120" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>44d</t>
         </is>
       </c>
       <c r="J120" s="17" t="inlineStr">
@@ -15643,12 +15967,12 @@
     <row r="121" ht="28" customHeight="1">
       <c r="B121" s="20" t="inlineStr">
         <is>
-          <t>140FC226R0002</t>
+          <t>140P5426R0015</t>
         </is>
       </c>
       <c r="C121" s="33" t="inlineStr">
         <is>
-          <t>Z--Levee Repair - MN</t>
+          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
         </is>
       </c>
       <c r="D121" s="20" t="inlineStr">
@@ -15673,12 +15997,12 @@
       </c>
       <c r="H121" s="20" t="inlineStr">
         <is>
-          <t>Jun 10, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I121" s="20" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>44d</t>
         </is>
       </c>
       <c r="J121" s="20" t="inlineStr">
@@ -15695,12 +16019,12 @@
     <row r="122" ht="28" customHeight="1">
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>140P5326R0019</t>
+          <t>140P5426R0017</t>
         </is>
       </c>
       <c r="C122" s="30" t="inlineStr">
         <is>
-          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D122" s="17" t="inlineStr">
@@ -15725,12 +16049,12 @@
       </c>
       <c r="H122" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I122" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44d</t>
         </is>
       </c>
       <c r="J122" s="17" t="inlineStr">
@@ -15745,52 +16069,52 @@
       </c>
     </row>
     <row r="123" ht="28" customHeight="1">
-      <c r="B123" s="37" t="inlineStr">
-        <is>
-          <t>36C25726B0007</t>
-        </is>
-      </c>
-      <c r="C123" s="25" t="inlineStr">
-        <is>
-          <t>Y1DA--CON Project 674A4-21-108 - Upgrade Fire Alarm  System Campus Wide  (Waco) (VA-25-00021609)</t>
-        </is>
-      </c>
-      <c r="D123" s="37" t="inlineStr">
-        <is>
-          <t>Waco, Texas</t>
-        </is>
-      </c>
-      <c r="E123" s="37" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F123" s="37" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G123" s="37" t="inlineStr">
-        <is>
-          <t>$2.5B</t>
-        </is>
-      </c>
-      <c r="H123" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I123" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J123" s="37" t="inlineStr">
+      <c r="B123" s="20" t="inlineStr">
+        <is>
+          <t>140FGA26R0024</t>
+        </is>
+      </c>
+      <c r="C123" s="33" t="inlineStr">
+        <is>
+          <t>Y--Sherburne NWR South Loop Autotour Rehab</t>
+        </is>
+      </c>
+      <c r="D123" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E123" s="20" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F123" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G123" s="20" t="inlineStr">
+        <is>
+          <t>$11.5M</t>
+        </is>
+      </c>
+      <c r="H123" s="20" t="inlineStr">
+        <is>
+          <t>Jul 27, 2026</t>
+        </is>
+      </c>
+      <c r="I123" s="20" t="inlineStr">
+        <is>
+          <t>47d</t>
+        </is>
+      </c>
+      <c r="J123" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K123" s="40" t="inlineStr">
+      <c r="K123" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15799,12 +16123,12 @@
     <row r="124" ht="28" customHeight="1">
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>W912HY26BA030</t>
+          <t>140L3726R0006</t>
         </is>
       </c>
       <c r="C124" s="30" t="inlineStr">
         <is>
-          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
+          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
         </is>
       </c>
       <c r="D124" s="17" t="inlineStr">
@@ -15814,7 +16138,7 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F124" s="17" t="inlineStr">
@@ -15824,17 +16148,17 @@
       </c>
       <c r="G124" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$19.0M</t>
         </is>
       </c>
       <c r="H124" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="I124" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>79d</t>
         </is>
       </c>
       <c r="J124" s="17" t="inlineStr">
@@ -15851,12 +16175,12 @@
     <row r="125" ht="28" customHeight="1">
       <c r="B125" s="20" t="inlineStr">
         <is>
-          <t>W912ES26BA013</t>
+          <t>36C25226Q0359</t>
         </is>
       </c>
       <c r="C125" s="33" t="inlineStr">
         <is>
-          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
+          <t>J059--Triennial Electical Panel Maintenance and Survey</t>
         </is>
       </c>
       <c r="D125" s="20" t="inlineStr">
@@ -15866,7 +16190,7 @@
       </c>
       <c r="E125" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F125" s="20" t="inlineStr">
@@ -15881,12 +16205,12 @@
       </c>
       <c r="H125" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jun 10, 2026</t>
         </is>
       </c>
       <c r="I125" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J125" s="20" t="inlineStr">
@@ -15903,12 +16227,12 @@
     <row r="126" ht="28" customHeight="1">
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>W912WJ26QA119</t>
+          <t>140FC226R0002</t>
         </is>
       </c>
       <c r="C126" s="30" t="inlineStr">
         <is>
-          <t>Storage Building Parking Lot Installation and Paving, Buffumville Lake, Charlton, MA</t>
+          <t>Z--Levee Repair - MN</t>
         </is>
       </c>
       <c r="D126" s="17" t="inlineStr">
@@ -15918,7 +16242,7 @@
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F126" s="17" t="inlineStr">
@@ -15928,17 +16252,17 @@
       </c>
       <c r="G126" s="17" t="inlineStr">
         <is>
-          <t>$175K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H126" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jun 10, 2026</t>
         </is>
       </c>
       <c r="I126" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J126" s="17" t="inlineStr">
@@ -15955,22 +16279,22 @@
     <row r="127" ht="28" customHeight="1">
       <c r="B127" s="20" t="inlineStr">
         <is>
-          <t>W911WN26BA008</t>
+          <t>140P5326R0019</t>
         </is>
       </c>
       <c r="C127" s="33" t="inlineStr">
         <is>
-          <t>Conemaugh Dam Gantry Crane Machinery Housing Roof Replacement</t>
+          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
         </is>
       </c>
       <c r="D127" s="20" t="inlineStr">
         <is>
-          <t>Saltsburg, Pennsylvania</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
@@ -15980,7 +16304,7 @@
       </c>
       <c r="G127" s="20" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H127" s="20" t="inlineStr">
@@ -16005,52 +16329,52 @@
       </c>
     </row>
     <row r="128" ht="28" customHeight="1">
-      <c r="B128" s="17" t="inlineStr">
-        <is>
-          <t>PANNWD26P0000028054</t>
-        </is>
-      </c>
-      <c r="C128" s="30" t="inlineStr">
-        <is>
-          <t>Levee Repair at MRLS L246</t>
-        </is>
-      </c>
-      <c r="D128" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E128" s="17" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F128" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G128" s="17" t="inlineStr">
-        <is>
-          <t>$3.0M</t>
-        </is>
-      </c>
-      <c r="H128" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I128" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J128" s="17" t="inlineStr">
+      <c r="B128" s="37" t="inlineStr">
+        <is>
+          <t>36C25726B0007</t>
+        </is>
+      </c>
+      <c r="C128" s="25" t="inlineStr">
+        <is>
+          <t>Y1DA--CON Project 674A4-21-108 - Upgrade Fire Alarm  System Campus Wide  (Waco) (VA-25-00021609)</t>
+        </is>
+      </c>
+      <c r="D128" s="37" t="inlineStr">
+        <is>
+          <t>Waco, Texas</t>
+        </is>
+      </c>
+      <c r="E128" s="37" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F128" s="37" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G128" s="37" t="inlineStr">
+        <is>
+          <t>$2.5B</t>
+        </is>
+      </c>
+      <c r="H128" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I128" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J128" s="37" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K128" s="32" t="inlineStr">
+      <c r="K128" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -16059,22 +16383,22 @@
     <row r="129" ht="28" customHeight="1">
       <c r="B129" s="20" t="inlineStr">
         <is>
-          <t>75H70126R00030</t>
+          <t>W912HY26BA030</t>
         </is>
       </c>
       <c r="C129" s="33" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
         </is>
       </c>
       <c r="D129" s="20" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F129" s="20" t="inlineStr">
@@ -16084,7 +16408,7 @@
       </c>
       <c r="G129" s="20" t="inlineStr">
         <is>
-          <t>$750K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H129" s="20" t="inlineStr">
@@ -16111,12 +16435,12 @@
     <row r="130" ht="28" customHeight="1">
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0028</t>
+          <t>W912ES26BA013</t>
         </is>
       </c>
       <c r="C130" s="30" t="inlineStr">
         <is>
-          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
+          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
         </is>
       </c>
       <c r="D130" s="17" t="inlineStr">
@@ -16126,7 +16450,7 @@
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F130" s="17" t="inlineStr">
@@ -16136,7 +16460,7 @@
       </c>
       <c r="G130" s="17" t="inlineStr">
         <is>
-          <t>$11.8M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H130" s="17" t="inlineStr">
@@ -16163,12 +16487,12 @@
     <row r="131" ht="28" customHeight="1">
       <c r="B131" s="20" t="inlineStr">
         <is>
-          <t>W9128F26RA107</t>
+          <t>W912WJ26QA119</t>
         </is>
       </c>
       <c r="C131" s="33" t="inlineStr">
         <is>
-          <t>Repair/Replace Mass Parking Apron Section V at Minot AFB North Dakota</t>
+          <t>Storage Building Parking Lot Installation and Paving, Buffumville Lake, Charlton, MA</t>
         </is>
       </c>
       <c r="D131" s="20" t="inlineStr">
@@ -16188,7 +16512,7 @@
       </c>
       <c r="G131" s="20" t="inlineStr">
         <is>
-          <t>$30.0M</t>
+          <t>$175K</t>
         </is>
       </c>
       <c r="H131" s="20" t="inlineStr">
@@ -16215,22 +16539,22 @@
     <row r="132" ht="28" customHeight="1">
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>12445526Q0069</t>
+          <t>W911WN26BA008</t>
         </is>
       </c>
       <c r="C132" s="30" t="inlineStr">
         <is>
-          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
+          <t>Conemaugh Dam Gantry Crane Machinery Housing Roof Replacement</t>
         </is>
       </c>
       <c r="D132" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Saltsburg, Pennsylvania</t>
         </is>
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F132" s="17" t="inlineStr">
@@ -16240,22 +16564,22 @@
       </c>
       <c r="G132" s="17" t="inlineStr">
         <is>
-          <t>$25K</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="H132" s="17" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I132" s="17" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J132" s="17" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K132" s="32" t="inlineStr">
@@ -16267,12 +16591,12 @@
     <row r="133" ht="28" customHeight="1">
       <c r="B133" s="20" t="inlineStr">
         <is>
-          <t>SP470525R002026</t>
+          <t>PANNWD26P0000028054</t>
         </is>
       </c>
       <c r="C133" s="33" t="inlineStr">
         <is>
-          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
+          <t>Levee Repair at MRLS L246</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
@@ -16282,7 +16606,7 @@
       </c>
       <c r="E133" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F133" s="20" t="inlineStr">
@@ -16292,22 +16616,22 @@
       </c>
       <c r="G133" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H133" s="20" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I133" s="20" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J133" s="20" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K133" s="35" t="inlineStr">
@@ -16319,57 +16643,317 @@
     <row r="134" ht="28" customHeight="1">
       <c r="B134" s="17" t="inlineStr">
         <is>
+          <t>75H70126R00030</t>
+        </is>
+      </c>
+      <c r="C134" s="30" t="inlineStr">
+        <is>
+          <t>Rosebud Lift Station Construction</t>
+        </is>
+      </c>
+      <c r="D134" s="17" t="inlineStr">
+        <is>
+          <t>Rosebud, South Dakota</t>
+        </is>
+      </c>
+      <c r="E134" s="17" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F134" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G134" s="17" t="inlineStr">
+        <is>
+          <t>$750K</t>
+        </is>
+      </c>
+      <c r="H134" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I134" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J134" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K134" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="28" customHeight="1">
+      <c r="B135" s="20" t="inlineStr">
+        <is>
+          <t>140FGA26R0028</t>
+        </is>
+      </c>
+      <c r="C135" s="33" t="inlineStr">
+        <is>
+          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
+        </is>
+      </c>
+      <c r="D135" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E135" s="20" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F135" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G135" s="20" t="inlineStr">
+        <is>
+          <t>$11.8M</t>
+        </is>
+      </c>
+      <c r="H135" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I135" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J135" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K135" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="28" customHeight="1">
+      <c r="B136" s="17" t="inlineStr">
+        <is>
+          <t>W9128F26RA107</t>
+        </is>
+      </c>
+      <c r="C136" s="30" t="inlineStr">
+        <is>
+          <t>Repair/Replace Mass Parking Apron Section V at Minot AFB North Dakota</t>
+        </is>
+      </c>
+      <c r="D136" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E136" s="17" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F136" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G136" s="17" t="inlineStr">
+        <is>
+          <t>$30.0M</t>
+        </is>
+      </c>
+      <c r="H136" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I136" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J136" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K136" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="28" customHeight="1">
+      <c r="B137" s="20" t="inlineStr">
+        <is>
+          <t>12445526Q0069</t>
+        </is>
+      </c>
+      <c r="C137" s="33" t="inlineStr">
+        <is>
+          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
+        </is>
+      </c>
+      <c r="D137" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E137" s="20" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F137" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G137" s="20" t="inlineStr">
+        <is>
+          <t>$25K</t>
+        </is>
+      </c>
+      <c r="H137" s="20" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="I137" s="20" t="inlineStr">
+        <is>
+          <t>14d</t>
+        </is>
+      </c>
+      <c r="J137" s="20" t="inlineStr">
+        <is>
+          <t>Special Notice</t>
+        </is>
+      </c>
+      <c r="K137" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="28" customHeight="1">
+      <c r="B138" s="17" t="inlineStr">
+        <is>
+          <t>SP470525R002026</t>
+        </is>
+      </c>
+      <c r="C138" s="30" t="inlineStr">
+        <is>
+          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
+        </is>
+      </c>
+      <c r="D138" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E138" s="17" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="F138" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G138" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H138" s="17" t="inlineStr">
+        <is>
+          <t>Jun 30, 2026</t>
+        </is>
+      </c>
+      <c r="I138" s="17" t="inlineStr">
+        <is>
+          <t>20d</t>
+        </is>
+      </c>
+      <c r="J138" s="17" t="inlineStr">
+        <is>
+          <t>Special Notice</t>
+        </is>
+      </c>
+      <c r="K138" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="28" customHeight="1">
+      <c r="B139" s="20" t="inlineStr">
+        <is>
           <t>W9127826RA025</t>
         </is>
       </c>
-      <c r="C134" s="30" t="inlineStr">
+      <c r="C139" s="33" t="inlineStr">
         <is>
           <t>Phillips Parkway Haul Route</t>
         </is>
       </c>
-      <c r="D134" s="17" t="inlineStr">
+      <c r="D139" s="20" t="inlineStr">
         <is>
           <t>Cape Canaveral, Florida</t>
         </is>
       </c>
-      <c r="E134" s="17" t="inlineStr">
+      <c r="E139" s="20" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F134" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G134" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H134" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I134" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J134" s="17" t="inlineStr">
+      <c r="F139" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G139" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H139" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I139" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J139" s="20" t="inlineStr">
         <is>
           <t>Special Notice</t>
         </is>
       </c>
-      <c r="K134" s="32" t="inlineStr">
+      <c r="K139" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K134"/>
+  <autoFilter ref="B5:K139"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -16504,6 +17088,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16516,7 +17105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K72"/>
+  <dimension ref="B2:K75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -16544,7 +17133,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="45" t="inlineStr">
         <is>
-          <t>NAICS: 213112 · 237110 · 237120 · 237130 · 238210 · 561210  ·  67 records  (13 SDVOSB)  ·  June 09, 2026</t>
+          <t>NAICS: 213112 · 237110 · 237120 · 237130 · 238210 · 561210  ·  70 records  (13 SDVOSB)  ·  June 09, 2026</t>
         </is>
       </c>
     </row>
@@ -17909,7 +18498,7 @@
       </c>
       <c r="C31" s="53" t="inlineStr">
         <is>
-          <t>PAIS WASTE WATER TANK REPLACEMENT</t>
+          <t>Y--PAIS WASTE WATER TANK REPLACEMENT</t>
         </is>
       </c>
       <c r="D31" s="54" t="inlineStr">
@@ -18273,7 +18862,7 @@
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>Y--GLBA REHAB WATERLINE</t>
+          <t>NM - SW NATIVE ARC - 5-Year BPA for Well Repair</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
@@ -18293,12 +18882,12 @@
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>13d</t>
         </is>
       </c>
       <c r="I38" s="17" t="inlineStr">
@@ -18320,12 +18909,12 @@
     <row r="39" ht="28" customHeight="1">
       <c r="B39" s="52" t="inlineStr">
         <is>
-          <t>213112 — Support Activities Oil &amp; Gas</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C39" s="53" t="inlineStr">
         <is>
-          <t>EO14398 UST ASSESSMENT &amp; REPORTING - GLBA</t>
+          <t>Y--GLBA REHAB WATERLINE</t>
         </is>
       </c>
       <c r="D39" s="54" t="inlineStr">
@@ -18372,12 +18961,12 @@
     <row r="40" ht="28" customHeight="1">
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>213112 — Support Activities Oil &amp; Gas</t>
         </is>
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>FTW506 Life Safety Repairs</t>
+          <t>EO14398 UST ASSESSMENT &amp; REPORTING - GLBA</t>
         </is>
       </c>
       <c r="D40" s="17" t="inlineStr">
@@ -18392,17 +18981,17 @@
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>$18.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Jun 24, 2026</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>15d</t>
+          <t>14d</t>
         </is>
       </c>
       <c r="I40" s="17" t="inlineStr">
@@ -18410,9 +18999,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J40" s="41" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
+      <c r="J40" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K40" s="32" t="inlineStr">
@@ -18429,12 +19018,12 @@
       </c>
       <c r="C41" s="53" t="inlineStr">
         <is>
-          <t>USMEPCOM Low Voltage Cable Removal</t>
+          <t>FTW506 Life Safety Repairs</t>
         </is>
       </c>
       <c r="D41" s="54" t="inlineStr">
         <is>
-          <t>North Chicago, Illinois</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E41" s="54" t="inlineStr">
@@ -18444,7 +19033,7 @@
       </c>
       <c r="F41" s="54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$18.0M</t>
         </is>
       </c>
       <c r="G41" s="54" t="inlineStr">
@@ -18476,17 +19065,17 @@
     <row r="42" ht="28" customHeight="1">
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
+          <t>USMEPCOM Low Voltage Cable Removal</t>
         </is>
       </c>
       <c r="D42" s="17" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia</t>
+          <t>North Chicago, Illinois</t>
         </is>
       </c>
       <c r="E42" s="17" t="inlineStr">
@@ -18528,17 +19117,17 @@
     <row r="43" ht="28" customHeight="1">
       <c r="B43" s="52" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C43" s="53" t="inlineStr">
         <is>
-          <t>Carpenter Substation Stage 03 South Dakota</t>
+          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
         </is>
       </c>
       <c r="D43" s="54" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Atlanta, Georgia</t>
         </is>
       </c>
       <c r="E43" s="54" t="inlineStr">
@@ -18553,12 +19142,12 @@
       </c>
       <c r="G43" s="54" t="inlineStr">
         <is>
-          <t>Jun 26, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="H43" s="54" t="inlineStr">
         <is>
-          <t>16d</t>
+          <t>15d</t>
         </is>
       </c>
       <c r="I43" s="54" t="inlineStr">
@@ -18580,17 +19169,17 @@
     <row r="44" ht="28" customHeight="1">
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C44" s="30" t="inlineStr">
         <is>
-          <t>FOSM - Replace Backflow Prevention Assemblies</t>
+          <t>Carpenter Substation Stage 03 South Dakota</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
         <is>
-          <t>Fort Smith, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E44" s="17" t="inlineStr">
@@ -18632,17 +19221,17 @@
     <row r="45" ht="28" customHeight="1">
       <c r="B45" s="52" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C45" s="53" t="inlineStr">
         <is>
-          <t>CT SWITCHGEAR REPLACEMENT STAMPEDE PP</t>
+          <t>FOSM - Replace Backflow Prevention Assemblies</t>
         </is>
       </c>
       <c r="D45" s="54" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Fort Smith, Arkansas</t>
         </is>
       </c>
       <c r="E45" s="54" t="inlineStr">
@@ -18657,12 +19246,12 @@
       </c>
       <c r="G45" s="54" t="inlineStr">
         <is>
-          <t>Jun 27, 2026</t>
+          <t>Jun 26, 2026</t>
         </is>
       </c>
       <c r="H45" s="54" t="inlineStr">
         <is>
-          <t>17d</t>
+          <t>16d</t>
         </is>
       </c>
       <c r="I45" s="54" t="inlineStr">
@@ -18684,12 +19273,12 @@
     <row r="46" ht="28" customHeight="1">
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C46" s="30" t="inlineStr">
         <is>
-          <t>Denison Substation Stage 10, Iowa</t>
+          <t>CT SWITCHGEAR REPLACEMENT STAMPEDE PP</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
@@ -18709,12 +19298,12 @@
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>Jun 29, 2026</t>
+          <t>Jun 27, 2026</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>19d</t>
+          <t>17d</t>
         </is>
       </c>
       <c r="I46" s="17" t="inlineStr">
@@ -18741,7 +19330,7 @@
       </c>
       <c r="C47" s="53" t="inlineStr">
         <is>
-          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
+          <t>Denison Substation Stage 10, Iowa</t>
         </is>
       </c>
       <c r="D47" s="54" t="inlineStr">
@@ -18756,7 +19345,7 @@
       </c>
       <c r="F47" s="54" t="inlineStr">
         <is>
-          <t>$23.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G47" s="54" t="inlineStr">
@@ -18788,12 +19377,12 @@
     <row r="48" ht="28" customHeight="1">
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C48" s="30" t="inlineStr">
         <is>
-          <t>Shenango River Lake Water Tank Rehabiliation</t>
+          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -18808,17 +19397,17 @@
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$23.0M</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jun 29, 2026</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>19d</t>
         </is>
       </c>
       <c r="I48" s="17" t="inlineStr">
@@ -18840,17 +19429,17 @@
     <row r="49" ht="28" customHeight="1">
       <c r="B49" s="52" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C49" s="53" t="inlineStr">
         <is>
-          <t>Electrical Upgrade for Brass Crusher</t>
+          <t>Shenango River Lake Water Tank Rehabiliation</t>
         </is>
       </c>
       <c r="D49" s="54" t="inlineStr">
         <is>
-          <t>Tampa, Florida</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E49" s="54" t="inlineStr">
@@ -18860,7 +19449,7 @@
       </c>
       <c r="F49" s="54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="G49" s="54" t="inlineStr">
@@ -18892,17 +19481,17 @@
     <row r="50" ht="28" customHeight="1">
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C50" s="30" t="inlineStr">
         <is>
-          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
+          <t>Electrical Upgrade for Brass Crusher</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Tampa, Florida</t>
         </is>
       </c>
       <c r="E50" s="17" t="inlineStr">
@@ -18912,17 +19501,17 @@
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>$11.4M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G50" s="17" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="I50" s="17" t="inlineStr">
@@ -18949,7 +19538,7 @@
       </c>
       <c r="C51" s="53" t="inlineStr">
         <is>
-          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
+          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
         </is>
       </c>
       <c r="D51" s="54" t="inlineStr">
@@ -18964,17 +19553,17 @@
       </c>
       <c r="F51" s="54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.4M</t>
         </is>
       </c>
       <c r="G51" s="54" t="inlineStr">
         <is>
-          <t>Jul 06, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="H51" s="54" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="I51" s="54" t="inlineStr">
@@ -18996,12 +19585,12 @@
     <row r="52" ht="28" customHeight="1">
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C52" s="30" t="inlineStr">
         <is>
-          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
+          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -19048,12 +19637,12 @@
     <row r="53" ht="28" customHeight="1">
       <c r="B53" s="52" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C53" s="53" t="inlineStr">
         <is>
-          <t>Base Operations Support Contract (BOSC) for Naval Air Weapons Station (NAWS) China Lake, California and Other Locations as Approved</t>
+          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
         </is>
       </c>
       <c r="D53" s="54" t="inlineStr">
@@ -19068,17 +19657,17 @@
       </c>
       <c r="F53" s="54" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G53" s="54" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="H53" s="54" t="inlineStr">
         <is>
-          <t>30d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="I53" s="54" t="inlineStr">
@@ -19100,12 +19689,12 @@
     <row r="54" ht="28" customHeight="1">
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C54" s="30" t="inlineStr">
         <is>
-          <t>J--GC26 FIRE ALARM SYSTEM REPLACEMENT</t>
+          <t xml:space="preserve">RELOCATABLE FACILITY (RFL) MAINTENANCE AND REPAIR SERVICES - EGLIN AFB </t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -19125,12 +19714,12 @@
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>30d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="I54" s="17" t="inlineStr">
@@ -19157,7 +19746,7 @@
       </c>
       <c r="C55" s="53" t="inlineStr">
         <is>
-          <t>CHINA LAKE BOSC - SOLICITATION - N6247326R0053</t>
+          <t>Base Operations Support Contract (BOSC) for Naval Air Weapons Station (NAWS) China Lake, California and Other Locations as Approved</t>
         </is>
       </c>
       <c r="D55" s="54" t="inlineStr">
@@ -19172,7 +19761,7 @@
       </c>
       <c r="F55" s="54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$47.0M</t>
         </is>
       </c>
       <c r="G55" s="54" t="inlineStr">
@@ -19204,12 +19793,12 @@
     <row r="56" ht="28" customHeight="1">
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>237120 — Oil &amp; Gas Pipeline</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C56" s="30" t="inlineStr">
         <is>
-          <t>Solicitation for Grand Forks Fueling System Repairs</t>
+          <t>J--GC26 FIRE ALARM SYSTEM REPLACEMENT</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -19256,12 +19845,12 @@
     <row r="57" ht="28" customHeight="1">
       <c r="B57" s="52" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C57" s="53" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>CHINA LAKE BOSC - SOLICITATION - N6247326R0053</t>
         </is>
       </c>
       <c r="D57" s="54" t="inlineStr">
@@ -19281,12 +19870,12 @@
       </c>
       <c r="G57" s="54" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 10, 2026</t>
         </is>
       </c>
       <c r="H57" s="54" t="inlineStr">
         <is>
-          <t>35d</t>
+          <t>30d</t>
         </is>
       </c>
       <c r="I57" s="54" t="inlineStr">
@@ -19294,9 +19883,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J57" s="42" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J57" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K57" s="55" t="inlineStr">
@@ -19308,17 +19897,17 @@
     <row r="58" ht="28" customHeight="1">
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237120 — Oil &amp; Gas Pipeline</t>
         </is>
       </c>
       <c r="C58" s="30" t="inlineStr">
         <is>
-          <t>Z--FOLS, Replace Alarm System &amp; Electrical Panel</t>
+          <t>Solicitation for Grand Forks Fueling System Repairs</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
         <is>
-          <t>Larned, Kansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E58" s="17" t="inlineStr">
@@ -19333,12 +19922,12 @@
       </c>
       <c r="G58" s="17" t="inlineStr">
         <is>
-          <t>Jun 10, 2026</t>
+          <t>Jul 10, 2026</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>30d</t>
         </is>
       </c>
       <c r="I58" s="17" t="inlineStr">
@@ -19346,9 +19935,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J58" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+      <c r="J58" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K58" s="32" t="inlineStr">
@@ -19360,17 +19949,17 @@
     <row r="59" ht="28" customHeight="1">
       <c r="B59" s="52" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C59" s="53" t="inlineStr">
         <is>
-          <t>USAO Schwartz Conference Room Display Upgrade</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="D59" s="54" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E59" s="54" t="inlineStr">
@@ -19385,22 +19974,22 @@
       </c>
       <c r="G59" s="54" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H59" s="54" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>35d</t>
         </is>
       </c>
       <c r="I59" s="54" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="J59" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="J59" s="42" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K59" s="55" t="inlineStr">
@@ -19417,12 +20006,12 @@
       </c>
       <c r="C60" s="30" t="inlineStr">
         <is>
-          <t>Z--WACO Emergency Generator</t>
+          <t>Z--FOLS, Replace Alarm System &amp; Electrical Panel</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t>Waco, Texas</t>
+          <t>Larned, Kansas</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
@@ -19432,22 +20021,22 @@
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>$62K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>Jun 10, 2026</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>8d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="J60" s="18" t="inlineStr">
@@ -19469,12 +20058,12 @@
       </c>
       <c r="C61" s="53" t="inlineStr">
         <is>
-          <t>J065--Variable Frequency Drive Maintenance</t>
+          <t>USAO Schwartz Conference Room Display Upgrade</t>
         </is>
       </c>
       <c r="D61" s="54" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>California</t>
         </is>
       </c>
       <c r="E61" s="54" t="inlineStr">
@@ -19489,12 +20078,12 @@
       </c>
       <c r="G61" s="54" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="H61" s="54" t="inlineStr">
         <is>
-          <t>12d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="I61" s="54" t="inlineStr">
@@ -19516,17 +20105,17 @@
     <row r="62" ht="28" customHeight="1">
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C62" s="30" t="inlineStr">
         <is>
-          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
+          <t>Z--WACO Emergency Generator</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>Baltimore, MD</t>
+          <t>Waco, Texas</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
@@ -19536,17 +20125,17 @@
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$62K</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>12d</t>
+          <t>8d</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
@@ -19568,17 +20157,17 @@
     <row r="63" ht="28" customHeight="1">
       <c r="B63" s="52" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C63" s="53" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>J065--Variable Frequency Drive Maintenance</t>
         </is>
       </c>
       <c r="D63" s="54" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E63" s="54" t="inlineStr">
@@ -19588,7 +20177,7 @@
       </c>
       <c r="F63" s="54" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G63" s="54" t="inlineStr">
@@ -19620,17 +20209,17 @@
     <row r="64" ht="28" customHeight="1">
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C64" s="30" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
@@ -19640,17 +20229,17 @@
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>$5.1M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>13d</t>
+          <t>12d</t>
         </is>
       </c>
       <c r="I64" s="17" t="inlineStr">
@@ -19672,17 +20261,17 @@
     <row r="65" ht="28" customHeight="1">
       <c r="B65" s="52" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C65" s="53" t="inlineStr">
         <is>
-          <t>Y--Beresford Substation Stage 11, South Dakota</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="D65" s="54" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="E65" s="54" t="inlineStr">
@@ -19692,17 +20281,17 @@
       </c>
       <c r="F65" s="54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$47.0M</t>
         </is>
       </c>
       <c r="G65" s="54" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="H65" s="54" t="inlineStr">
         <is>
-          <t>35d</t>
+          <t>12d</t>
         </is>
       </c>
       <c r="I65" s="54" t="inlineStr">
@@ -19710,9 +20299,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J65" s="42" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J65" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K65" s="55" t="inlineStr">
@@ -19724,17 +20313,17 @@
     <row r="66" ht="28" customHeight="1">
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C66" s="30" t="inlineStr">
         <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
+          <t>B16 PLC Replacement</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t>Royal, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
@@ -19744,17 +20333,17 @@
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$5.1M</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>35d</t>
+          <t>13d</t>
         </is>
       </c>
       <c r="I66" s="17" t="inlineStr">
@@ -19762,9 +20351,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J66" s="42" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J66" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K66" s="32" t="inlineStr">
@@ -19776,12 +20365,12 @@
     <row r="67" ht="28" customHeight="1">
       <c r="B67" s="52" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C67" s="53" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>Y--Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="D67" s="54" t="inlineStr">
@@ -19801,12 +20390,12 @@
       </c>
       <c r="G67" s="54" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H67" s="54" t="inlineStr">
         <is>
-          <t>44d</t>
+          <t>35d</t>
         </is>
       </c>
       <c r="I67" s="54" t="inlineStr">
@@ -19828,17 +20417,17 @@
     <row r="68" ht="28" customHeight="1">
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C68" s="30" t="inlineStr">
         <is>
-          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
@@ -19848,17 +20437,17 @@
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>79d</t>
+          <t>35d</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
@@ -19880,12 +20469,12 @@
     <row r="69" ht="28" customHeight="1">
       <c r="B69" s="52" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C69" s="53" t="inlineStr">
         <is>
-          <t>J059--Triennial Electical Panel Maintenance and Survey</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D69" s="54" t="inlineStr">
@@ -19905,12 +20494,12 @@
       </c>
       <c r="G69" s="54" t="inlineStr">
         <is>
-          <t>Jun 10, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="H69" s="54" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>44d</t>
         </is>
       </c>
       <c r="I69" s="54" t="inlineStr">
@@ -19918,9 +20507,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J69" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+      <c r="J69" s="42" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K69" s="55" t="inlineStr">
@@ -19937,7 +20526,7 @@
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
@@ -19957,12 +20546,12 @@
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44d</t>
         </is>
       </c>
       <c r="I70" s="17" t="inlineStr">
@@ -19972,7 +20561,7 @@
       </c>
       <c r="J70" s="42" t="inlineStr">
         <is>
-          <t>Pre-Sol</t>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K70" s="32" t="inlineStr">
@@ -19984,17 +20573,17 @@
     <row r="71" ht="28" customHeight="1">
       <c r="B71" s="52" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C71" s="53" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
         </is>
       </c>
       <c r="D71" s="54" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E71" s="54" t="inlineStr">
@@ -20004,17 +20593,17 @@
       </c>
       <c r="F71" s="54" t="inlineStr">
         <is>
-          <t>$750K</t>
+          <t>$19.0M</t>
         </is>
       </c>
       <c r="G71" s="54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="H71" s="54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>79d</t>
         </is>
       </c>
       <c r="I71" s="54" t="inlineStr">
@@ -20024,7 +20613,7 @@
       </c>
       <c r="J71" s="42" t="inlineStr">
         <is>
-          <t>Pre-Sol</t>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K71" s="55" t="inlineStr">
@@ -20036,57 +20625,213 @@
     <row r="72" ht="28" customHeight="1">
       <c r="B72" s="16" t="inlineStr">
         <is>
+          <t>238210 — Electrical Contractors</t>
+        </is>
+      </c>
+      <c r="C72" s="30" t="inlineStr">
+        <is>
+          <t>J059--Triennial Electical Panel Maintenance and Survey</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>Jun 10, 2026</t>
+        </is>
+      </c>
+      <c r="H72" s="17" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="J72" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="B73" s="52" t="inlineStr">
+        <is>
+          <t>237110 — Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="C73" s="53" t="inlineStr">
+        <is>
+          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+        </is>
+      </c>
+      <c r="D73" s="54" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E73" s="54" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F73" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="54" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="J73" s="42" t="inlineStr">
+        <is>
+          <t>Pre-Sol</t>
+        </is>
+      </c>
+      <c r="K73" s="55" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>237110 — Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="C74" s="30" t="inlineStr">
+        <is>
+          <t>Rosebud Lift Station Construction</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>Rosebud, South Dakota</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>$750K</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="J74" s="42" t="inlineStr">
+        <is>
+          <t>Pre-Sol</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="28" customHeight="1">
+      <c r="B75" s="52" t="inlineStr">
+        <is>
           <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
-      <c r="C72" s="30" t="inlineStr">
+      <c r="C75" s="53" t="inlineStr">
         <is>
           <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
         </is>
       </c>
-      <c r="D72" s="17" t="inlineStr">
+      <c r="D75" s="54" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E72" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="F72" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="17" t="inlineStr">
+      <c r="E75" s="54" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F75" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="54" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="H72" s="17" t="inlineStr">
+      <c r="H75" s="54" t="inlineStr">
         <is>
           <t>20d</t>
         </is>
       </c>
-      <c r="I72" s="17" t="inlineStr">
+      <c r="I75" s="54" t="inlineStr">
         <is>
           <t>Special Notice</t>
         </is>
       </c>
-      <c r="J72" s="41" t="inlineStr">
+      <c r="J75" s="41" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="K72" s="32" t="inlineStr">
+      <c r="K75" s="55" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K72"/>
+  <autoFilter ref="B5:K75"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -20159,6 +20904,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
